--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3304" uniqueCount="647">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3290" uniqueCount="635">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T12:31:04+00:00</t>
+    <t>2025-03-04T08:19:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -282,7 +282,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}vs-2:If there is no component or hasMember element then either a value[x] or a data absent reason must be present. {(component.empty() and hasMember.empty()) implies (dataAbsentReason.exists() or value.exists())}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}vs-2:If there is no component or hasMember element then either a value[x] or a data absent reason must be present. {(component.empty() and hasMember.empty()) implies (dataAbsentReason.exists() or value.exists())}</t>
   </si>
   <si>
     <t>Event</t>
@@ -338,338 +338,335 @@
     <t>Resource.meta</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
+  </si>
+  <si>
+    <t>Observation.meta.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Observation.meta.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Observation.meta.versionId</t>
+  </si>
+  <si>
+    <t>Version specific identifier</t>
+  </si>
+  <si>
+    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
+  </si>
+  <si>
+    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
+  </si>
+  <si>
+    <t>Meta.versionId</t>
+  </si>
+  <si>
+    <t>Observation.meta.lastUpdated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>When the resource version last changed</t>
+  </si>
+  <si>
+    <t>When the resource last changed - e.g. when the version changed.</t>
+  </si>
+  <si>
+    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
+  </si>
+  <si>
+    <t>Meta.lastUpdated</t>
+  </si>
+  <si>
+    <t>Observation.meta.source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uri
+</t>
+  </si>
+  <si>
+    <t>Uri identifiant les systèmes tiers ayant envoyé la ressource.
+L’uri est sous la forme d’un oid : « urn:oid:xx.xx.xx »</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
+    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
+This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
+  </si>
+  <si>
+    <t>Meta.source</t>
+  </si>
+  <si>
+    <t>Observation.meta.profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(StructureDefinition)
+</t>
+  </si>
+  <si>
+    <t>Profiles this resource claims to conform to</t>
+  </si>
+  <si>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+  </si>
+  <si>
+    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
+  </si>
+  <si>
+    <t>Meta.profile</t>
+  </si>
+  <si>
+    <t>Observation.meta.security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Security Labels applied to this resource</t>
+  </si>
+  <si>
+    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
+  </si>
+  <si>
+    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+  </si>
+  <si>
+    <t>Meta.security</t>
+  </si>
+  <si>
+    <t>Observation.meta.tag</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+  </si>
+  <si>
+    <t>Meta.tag</t>
+  </si>
+  <si>
+    <t>Observation.implicitRules</t>
+  </si>
+  <si>
+    <t>A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+  </si>
+  <si>
+    <t>Resource.implicitRules</t>
+  </si>
+  <si>
+    <t>Observation.language</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code
+</t>
+  </si>
+  <si>
+    <t>Language of the resource content</t>
+  </si>
+  <si>
+    <t>The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+  </si>
+  <si>
+    <t>preferred</t>
+  </si>
+  <si>
+    <t>A human language.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
+  </si>
+  <si>
+    <t>Resource.language</t>
+  </si>
+  <si>
+    <t>Observation.text</t>
+  </si>
+  <si>
+    <t>narrative
+htmlxhtmldisplay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narrative
+</t>
+  </si>
+  <si>
+    <t>Text summary of the resource, for human interpretation</t>
+  </si>
+  <si>
+    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+  </si>
+  <si>
+    <t>DomainResource.text</t>
+  </si>
+  <si>
+    <t>Act.text?</t>
+  </si>
+  <si>
+    <t>Observation.contained</t>
+  </si>
+  <si>
+    <t>inline resources
+anonymous resourcescontained resources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resource
+</t>
+  </si>
+  <si>
+    <t>Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+  </si>
+  <si>
+    <t>DomainResource.contained</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Observation.extension</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>Observation.extension:supportingInfo</t>
+  </si>
+  <si>
+    <t>supportingInfo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {workflow-supportingInfo}
+</t>
+  </si>
+  <si>
+    <t>Other information that may be relevant to this event.</t>
+  </si>
+  <si>
+    <t>Other resources *from the patient record* that may be relevant to the event.  The information from these resources was either used to create the instance or is provided to help with its interpretation.  This extension **should not** be used if more specific  inline elements  or extensions are available.  For example, use `Observation.hasMember`  instead of supportingInformation for  representing the members of an Observation panel.</t>
+  </si>
+  <si>
+    <t>Observation.extension:MesReasonForMeasurement</t>
+  </si>
+  <si>
+    <t>MesReasonForMeasurement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-reason-for-measurement}
+</t>
+  </si>
+  <si>
+    <t>Motif de la mesure</t>
+  </si>
+  <si>
+    <t>Extension du Motif de la mesure, exprimé en texte libre.</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Observation.meta.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Observation.meta.extension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>Observation.meta.versionId</t>
-  </si>
-  <si>
-    <t>Version specific identifier</t>
-  </si>
-  <si>
-    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
-  </si>
-  <si>
-    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
-  </si>
-  <si>
-    <t>Meta.versionId</t>
-  </si>
-  <si>
-    <t>Observation.meta.lastUpdated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">instant
-</t>
-  </si>
-  <si>
-    <t>When the resource version last changed</t>
-  </si>
-  <si>
-    <t>When the resource last changed - e.g. when the version changed.</t>
-  </si>
-  <si>
-    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
-  </si>
-  <si>
-    <t>Meta.lastUpdated</t>
-  </si>
-  <si>
-    <t>Observation.meta.source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">uri
-</t>
-  </si>
-  <si>
-    <t>Uri identifiant les systèmes tiers ayant envoyé la ressource.
-L’uri est sous la forme d’un oid : « urn:oid:xx.xx.xx »</t>
-  </si>
-  <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
-  </si>
-  <si>
-    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
-This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
-  </si>
-  <si>
-    <t>Meta.source</t>
-  </si>
-  <si>
-    <t>Observation.meta.profile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
-</t>
-  </si>
-  <si>
-    <t>Profiles this resource claims to conform to</t>
-  </si>
-  <si>
-    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
-  </si>
-  <si>
-    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
-  </si>
-  <si>
-    <t>Meta.profile</t>
-  </si>
-  <si>
-    <t>Observation.meta.security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Security Labels applied to this resource</t>
-  </si>
-  <si>
-    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
-  </si>
-  <si>
-    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
-  </si>
-  <si>
-    <t>Meta.security</t>
-  </si>
-  <si>
-    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
-  </si>
-  <si>
-    <t>CV</t>
-  </si>
-  <si>
-    <t>Observation.meta.tag</t>
-  </si>
-  <si>
-    <t>Tags applied to this resource</t>
-  </si>
-  <si>
-    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
-  </si>
-  <si>
-    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
-  </si>
-  <si>
-    <t>Meta.tag</t>
-  </si>
-  <si>
-    <t>Observation.implicitRules</t>
-  </si>
-  <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
-  </si>
-  <si>
-    <t>Resource.implicitRules</t>
-  </si>
-  <si>
-    <t>Observation.language</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
-  </si>
-  <si>
-    <t>preferred</t>
-  </si>
-  <si>
-    <t>A human language.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
-  </si>
-  <si>
-    <t>Resource.language</t>
-  </si>
-  <si>
-    <t>Observation.text</t>
-  </si>
-  <si>
-    <t>narrative
-htmlxhtmldisplay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narrative
-</t>
-  </si>
-  <si>
-    <t>Text summary of the resource, for human interpretation</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
-  </si>
-  <si>
-    <t>DomainResource.text</t>
-  </si>
-  <si>
-    <t>Act.text?</t>
-  </si>
-  <si>
-    <t>Observation.contained</t>
-  </si>
-  <si>
-    <t>inline resources
-anonymous resourcescontained resources</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource
-</t>
-  </si>
-  <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
-  </si>
-  <si>
-    <t>DomainResource.contained</t>
-  </si>
-  <si>
-    <t>Observation.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>Observation.extension:supportingInfo</t>
-  </si>
-  <si>
-    <t>supportingInfo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {workflow-supportingInfo}
-</t>
-  </si>
-  <si>
-    <t>Other information that may be relevant to this event.</t>
-  </si>
-  <si>
-    <t>Other resources *from the patient record* that may be relevant to the event.  The information from these resources was either used to create the instance or is provided to help with its interpretation.  This extension **should not** be used if more specific  inline elements  or extensions are available.  For example, use `Observation.hasMember`  instead of supportingInformation for  representing the members of an Observation panel.</t>
-  </si>
-  <si>
-    <t>Observation.extension:MesReasonForMeasurement</t>
-  </si>
-  <si>
-    <t>MesReasonForMeasurement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-reason-for-measurement}
-</t>
-  </si>
-  <si>
-    <t>Motif de la mesure</t>
-  </si>
-  <si>
-    <t>Extension du Motif de la mesure, exprimé en texte libre.</t>
-  </si>
-  <si>
     <t>Observation.modifierExtension</t>
   </si>
   <si>
@@ -680,7 +677,7 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -731,14 +728,7 @@
     <t>A plan, proposal or order that is fulfilled in whole or in part by this event.  For example, a MedicationRequest may require a patient to have laboratory test performed before  it is dispensed.</t>
   </si>
   <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
     <t>Allows tracing of authorization for the event and tracking whether proposals/recommendations were acted upon.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
   </si>
   <si>
     <t>Event.basedOn</t>
@@ -767,7 +757,7 @@
     <t>A larger event of which this particular Observation is a component or step.  For example,  an observation as part of a procedure.</t>
   </si>
   <si>
-    <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
+    <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
   </si>
   <si>
     <t>Event.partOf</t>
@@ -795,9 +785,6 @@
   </si>
   <si>
     <t>required</t>
-  </si>
-  <si>
-    <t>Codes providing the status of an observation.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/observation-status|4.0.1</t>
@@ -847,9 +834,6 @@
 value:coding.system}</t>
   </si>
   <si>
-    <t>CE/CNE/CWE</t>
-  </si>
-  <si>
     <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
   </si>
   <si>
@@ -977,9 +961,6 @@
   </si>
   <si>
     <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>Need to refer to a particular code in the system.</t>
@@ -1194,7 +1175,7 @@
     <t>The actual focus of an observation when it is not the patient of record representing something or someone associated with the patient such as a spouse, parent, fetus, or donor. For example, fetus observations in a mother's record.  The focus of an observation could also be an existing condition,  an intervention, the subject's diet,  another observation of the subject,  or a body structure such as tumor or implanted device.   An example use case would be using the Observation resource to capture whether the mother is trained to change her child's tracheostomy tube. In this example, the child is the patient of record and the mother is the focus.</t>
   </si>
   <si>
-    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4/extension-observation-focuscode.html).</t>
+    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/extension-observation-focuscode.html).</t>
   </si>
   <si>
     <t>participation[typeCode=SBJ]</t>
@@ -1252,14 +1233,14 @@
     <t>Often just a dateTime for Vital Signs.</t>
   </si>
   <si>
-    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
+    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
   </si>
   <si>
     <t>Knowing when an observation was deemed true is important to its relevance as well as determining trends.</t>
   </si>
   <si>
-    <t>ele-1
-vs-1</t>
+    <t xml:space="preserve">vs-1
+</t>
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
@@ -1287,7 +1268,7 @@
     <t>The date and time this version of the observation was made available to providers, typically after the results have been reviewed and verified.</t>
   </si>
   <si>
-    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
+    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
   </si>
   <si>
     <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
@@ -1337,7 +1318,7 @@
     <t>Vital Signs value are recorded using the Quantity data type. For supporting observations such as Cuff size could use other datatypes such as CodeableConcept.</t>
   </si>
   <si>
-    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
+    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/observation.html#notes) below.</t>
   </si>
   <si>
     <t>9. SHALL contain exactly one [1..1] value with @xsi:type="PQ" (CONF:7305).</t>
@@ -1347,8 +1328,8 @@
 </t>
   </si>
   <si>
-    <t>ele-1
-obs-7vs-2</t>
+    <t>obs-7
+vs-2</t>
   </si>
   <si>
     <t>&lt; 441742003 |Evaluation finding|</t>
@@ -1460,9 +1441,6 @@
     <t>The identification of the system that provides the coded form of the unit.</t>
   </si>
   <si>
-    <t>see http://en.wikipedia.org/wiki/Uniform_resource_identifier</t>
-  </si>
-  <si>
     <t>Need to know the system that defines the coded form of the unit.</t>
   </si>
   <si>
@@ -1472,8 +1450,8 @@
     <t>Quantity.system</t>
   </si>
   <si>
-    <t>ele-1
-qty-3</t>
+    <t xml:space="preserve">qty-3
+</t>
   </si>
   <si>
     <t>CO.codeSystem, PQ.translation.codeSystem</t>
@@ -1522,8 +1500,8 @@
     <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
   </si>
   <si>
-    <t>ele-1
-obs-6vs-2</t>
+    <t>obs-6
+vs-2</t>
   </si>
   <si>
     <t>value.nullFlavor</t>
@@ -1601,7 +1579,7 @@
   </si>
   <si>
     <t>Only used if not implicit in code found in Observation.code.  In many systems, this may be represented as a related observation instead of an inline component.   
-If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
+If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/extension-bodysite.html).</t>
   </si>
   <si>
     <t>Codes describing anatomical locations. May include laterality.</t>
@@ -1771,15 +1749,8 @@
     <t>The value of the low bound of the reference range.  The low bound of the reference range endpoint is inclusive of the value (e.g.  reference range is &gt;=5 - &lt;=9). If the low bound is omitted,  it is assumed to be meaningless (e.g. reference range is &lt;=2.3).</t>
   </si>
   <si>
-    <t>The context of use may frequently define what kind of quantity this is and therefore what kind of units can be used. The context of use may also restrict the values for the comparator.</t>
-  </si>
-  <si>
-    <t>ele-1
-obs-3</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-qty-3:If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
+    <t xml:space="preserve">obs-3
+</t>
   </si>
   <si>
     <t>OBX-7</t>
@@ -1867,17 +1838,7 @@
     <t>The age at which this reference range is applicable. This is a neonatal age (e.g. number of weeks at term) if the meaning says so.</t>
   </si>
   <si>
-    <t>The stated low and high value are assumed to have arbitrarily high precision when it comes to determining which values are in the range. I.e. 1.99 is not in the range 2 -&gt; 3.</t>
-  </si>
-  <si>
     <t>Some analytes vary greatly over age.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-rng-2:If present, low SHALL have a lower value than high {low.empty() or high.empty() or (low &lt;= high)}</t>
-  </si>
-  <si>
-    <t>NR and also possibly SN (but see also quantity)</t>
   </si>
   <si>
     <t>outboundRelationship[typeCode=PRCN].targetObservationCriterion[code="age"].value</t>
@@ -1908,7 +1869,7 @@
     <t>Used when reporting vital signs panel components.</t>
   </si>
   <si>
-    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
+    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
   </si>
   <si>
     <t>Relationships established by OBX-4 usage</t>
@@ -1930,7 +1891,7 @@
     <t>The target resource that represents a measurement from which this observation value is derived. For example, a calculated anion gap or a fetal measurement based on an ultrasound image.</t>
   </si>
   <si>
-    <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.</t>
+    <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/observation.html#obsgrouping) below.</t>
   </si>
   <si>
     <t>.targetObservation</t>
@@ -1942,7 +1903,7 @@
     <t>Used when reporting systolic and diastolic blood pressure.</t>
   </si>
   <si>
-    <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
+    <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](http://hl7.org/fhir/observation.html#notes) below.</t>
   </si>
   <si>
     <t>Component observations share the same attributes in the Observation resource as the primary observation and are always treated a part of a single observation (they are not separable).   However, the reference range for the primary observation value is not inherited by the component values and is required when appropriate for each component observation.</t>
@@ -1999,7 +1960,7 @@
     <t>Vital Sign Value recorded with UCUM.</t>
   </si>
   <si>
-    <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
+    <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/observation.html#notes) below.</t>
   </si>
   <si>
     <t>Common UCUM units for recording Vital Signs.</t>
@@ -2008,8 +1969,8 @@
     <t>http://hl7.org/fhir/ValueSet/ucum-vitals-common|4.0.1</t>
   </si>
   <si>
-    <t>ele-1
-vs-3</t>
+    <t xml:space="preserve">vs-3
+</t>
   </si>
   <si>
     <t>363714003 |Interprets| &lt; 441742003 |Evaluation finding|</t>
@@ -2028,8 +1989,8 @@
 The alternate way is to use the value element for actual observations and use the explicit dataAbsentReason element to record exceptional values.  For example, the dataAbsentReason code "error" could be used when the measurement was not completed.  Because of these options, use-case agreements are required to interpret general observations for exceptional values.</t>
   </si>
   <si>
-    <t>ele-1
-obs-6vs-3</t>
+    <t>obs-6
+vs-3</t>
   </si>
   <si>
     <t>Observation.component.interpretation</t>
@@ -2866,11 +2827,11 @@
         <v>93</v>
       </c>
       <c r="AI4" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ4" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK4" t="s" s="2">
         <v>82</v>
       </c>
@@ -2881,7 +2842,7 @@
         <v>82</v>
       </c>
       <c r="AN4" t="s" s="2">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="AO4" t="s" s="2">
         <v>82</v>
@@ -2892,10 +2853,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2918,13 +2879,13 @@
         <v>82</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L5" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M5" t="s" s="2">
         <v>109</v>
-      </c>
-      <c r="L5" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="M5" t="s" s="2">
-        <v>111</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -2975,7 +2936,7 @@
         <v>82</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>80</v>
@@ -2999,7 +2960,7 @@
         <v>82</v>
       </c>
       <c r="AN5" t="s" s="2">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AO5" t="s" s="2">
         <v>82</v>
@@ -3010,14 +2971,14 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
@@ -3036,16 +2997,16 @@
         <v>82</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L6" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="M6" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>117</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>119</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -3083,19 +3044,19 @@
         <v>82</v>
       </c>
       <c r="AB6" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE6" t="s" s="2">
         <v>120</v>
       </c>
-      <c r="AC6" t="s" s="2">
+      <c r="AF6" t="s" s="2">
         <v>121</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>80</v>
@@ -3104,10 +3065,10 @@
         <v>81</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>82</v>
@@ -3119,7 +3080,7 @@
         <v>82</v>
       </c>
       <c r="AN6" t="s" s="2">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="AO6" t="s" s="2">
         <v>82</v>
@@ -3130,10 +3091,10 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -3159,13 +3120,13 @@
         <v>95</v>
       </c>
       <c r="L7" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="M7" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="N7" t="s" s="2">
         <v>126</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>128</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -3215,7 +3176,7 @@
         <v>82</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
@@ -3224,11 +3185,11 @@
         <v>93</v>
       </c>
       <c r="AI7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ7" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK7" t="s" s="2">
         <v>82</v>
       </c>
@@ -3239,7 +3200,7 @@
         <v>82</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>82</v>
@@ -3250,10 +3211,10 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -3276,16 +3237,16 @@
         <v>94</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="M8" t="s" s="2">
         <v>131</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>134</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -3335,7 +3296,7 @@
         <v>82</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -3344,11 +3305,11 @@
         <v>93</v>
       </c>
       <c r="AI8" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ8" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ8" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK8" t="s" s="2">
         <v>82</v>
       </c>
@@ -3359,7 +3320,7 @@
         <v>82</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>82</v>
@@ -3370,10 +3331,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -3396,16 +3357,16 @@
         <v>94</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>140</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -3455,7 +3416,7 @@
         <v>82</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -3464,11 +3425,11 @@
         <v>93</v>
       </c>
       <c r="AI9" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ9" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ9" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK9" t="s" s="2">
         <v>82</v>
       </c>
@@ -3479,7 +3440,7 @@
         <v>82</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>82</v>
@@ -3490,10 +3451,10 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -3516,16 +3477,16 @@
         <v>94</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="L10" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="L10" t="s" s="2">
+      <c r="N10" t="s" s="2">
         <v>144</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>146</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -3575,7 +3536,7 @@
         <v>82</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -3584,11 +3545,11 @@
         <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ10" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ10" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK10" t="s" s="2">
         <v>82</v>
       </c>
@@ -3599,7 +3560,7 @@
         <v>82</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>82</v>
@@ -3610,10 +3571,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3636,16 +3597,16 @@
         <v>94</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="L11" t="s" s="2">
+      <c r="N11" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -3671,31 +3632,31 @@
         <v>82</v>
       </c>
       <c r="X11" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="Y11" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="Z11" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="Y11" t="s" s="2">
+      <c r="AA11" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB11" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC11" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD11" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE11" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF11" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="Z11" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="AA11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF11" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3704,11 +3665,11 @@
         <v>81</v>
       </c>
       <c r="AI11" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ11" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ11" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK11" t="s" s="2">
         <v>82</v>
       </c>
@@ -3716,10 +3677,10 @@
         <v>82</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>158</v>
+        <v>82</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>82</v>
@@ -3730,10 +3691,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3756,16 +3717,16 @@
         <v>94</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3791,13 +3752,13 @@
         <v>82</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>82</v>
@@ -3815,7 +3776,7 @@
         <v>82</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3824,11 +3785,11 @@
         <v>81</v>
       </c>
       <c r="AI12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ12" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ12" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK12" t="s" s="2">
         <v>82</v>
       </c>
@@ -3836,10 +3797,10 @@
         <v>82</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>158</v>
+        <v>82</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>82</v>
@@ -3850,10 +3811,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3876,16 +3837,16 @@
         <v>94</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3935,7 +3896,7 @@
         <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3944,11 +3905,11 @@
         <v>93</v>
       </c>
       <c r="AI13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ13" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK13" t="s" s="2">
         <v>82</v>
       </c>
@@ -3959,7 +3920,7 @@
         <v>82</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>82</v>
@@ -3970,10 +3931,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3996,16 +3957,16 @@
         <v>82</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -4031,13 +3992,13 @@
         <v>82</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>82</v>
@@ -4055,7 +4016,7 @@
         <v>82</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -4064,11 +4025,11 @@
         <v>93</v>
       </c>
       <c r="AI14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ14" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK14" t="s" s="2">
         <v>82</v>
       </c>
@@ -4079,7 +4040,7 @@
         <v>82</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>82</v>
@@ -4090,14 +4051,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -4116,16 +4077,16 @@
         <v>82</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4175,7 +4136,7 @@
         <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -4184,11 +4145,11 @@
         <v>93</v>
       </c>
       <c r="AI15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ15" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK15" t="s" s="2">
         <v>82</v>
       </c>
@@ -4199,7 +4160,7 @@
         <v>82</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>82</v>
@@ -4210,14 +4171,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4236,16 +4197,16 @@
         <v>82</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4295,7 +4256,7 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -4319,7 +4280,7 @@
         <v>82</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>107</v>
+        <v>192</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>82</v>
@@ -4330,14 +4291,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4356,17 +4317,15 @@
         <v>82</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>117</v>
+        <v>194</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>119</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>82</v>
@@ -4403,19 +4362,17 @@
         <v>82</v>
       </c>
       <c r="AB17" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AC17" s="2"/>
+      <c r="AD17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE17" t="s" s="2">
         <v>120</v>
       </c>
-      <c r="AC17" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>122</v>
-      </c>
       <c r="AF17" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4424,10 +4381,10 @@
         <v>81</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>82</v>
@@ -4439,7 +4396,7 @@
         <v>82</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>82</v>
@@ -4450,13 +4407,13 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>82</v>
@@ -4478,13 +4435,13 @@
         <v>82</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="L18" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4535,7 +4492,7 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4544,10 +4501,10 @@
         <v>81</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>82</v>
@@ -4570,13 +4527,13 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>82</v>
@@ -4598,13 +4555,13 @@
         <v>82</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="L19" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4655,7 +4612,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4664,10 +4621,10 @@
         <v>81</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>105</v>
+        <v>207</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>82</v>
@@ -4690,14 +4647,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4716,19 +4673,19 @@
         <v>82</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O20" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>82</v>
@@ -4765,19 +4722,19 @@
         <v>82</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>121</v>
+        <v>82</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4786,10 +4743,10 @@
         <v>81</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>82</v>
@@ -4801,7 +4758,7 @@
         <v>82</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>107</v>
+        <v>192</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>82</v>
@@ -4812,10 +4769,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4838,17 +4795,17 @@
         <v>94</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>82</v>
@@ -4897,7 +4854,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4906,25 +4863,25 @@
         <v>81</v>
       </c>
       <c r="AI21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ21" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK21" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="AL21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM21" t="s" s="2">
+      <c r="AN21" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="AN21" t="s" s="2">
+      <c r="AO21" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>82</v>
@@ -4932,14 +4889,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4958,19 +4915,17 @@
         <v>94</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" s="2"/>
+      <c r="O22" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>82</v>
@@ -5019,7 +4974,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -5028,22 +4983,22 @@
         <v>81</v>
       </c>
       <c r="AI22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ22" t="s" s="2">
+      <c r="AK22" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AN22" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="AK22" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="AL22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>82</v>
@@ -5054,14 +5009,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -5080,16 +5035,16 @@
         <v>94</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="N23" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="L23" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -5139,7 +5094,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -5148,22 +5103,22 @@
         <v>81</v>
       </c>
       <c r="AI23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ23" t="s" s="2">
-        <v>230</v>
-      </c>
       <c r="AK23" t="s" s="2">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>82</v>
@@ -5174,10 +5129,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5200,19 +5155,19 @@
         <v>94</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="O24" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -5237,13 +5192,11 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="Y24" t="s" s="2">
-        <v>249</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
@@ -5261,7 +5214,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>93</v>
@@ -5270,25 +5223,25 @@
         <v>93</v>
       </c>
       <c r="AI24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ24" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK24" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AN24" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AO24" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>82</v>
@@ -5296,10 +5249,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5322,19 +5275,19 @@
         <v>82</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="O25" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="L25" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -5359,29 +5312,29 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="AC25" s="2"/>
       <c r="AD25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5390,11 +5343,11 @@
         <v>81</v>
       </c>
       <c r="AI25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ25" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK25" t="s" s="2">
         <v>82</v>
       </c>
@@ -5402,13 +5355,13 @@
         <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>265</v>
+        <v>82</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>82</v>
@@ -5416,13 +5369,13 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>82</v>
@@ -5444,19 +5397,19 @@
         <v>82</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="O26" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="L26" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -5481,13 +5434,13 @@
         <v>82</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
@@ -5505,7 +5458,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5514,11 +5467,11 @@
         <v>81</v>
       </c>
       <c r="AI26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ26" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK26" t="s" s="2">
         <v>82</v>
       </c>
@@ -5526,13 +5479,13 @@
         <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>265</v>
+        <v>82</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>82</v>
@@ -5540,10 +5493,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5566,13 +5519,13 @@
         <v>82</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>109</v>
-      </c>
-      <c r="L27" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>111</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5623,7 +5576,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5647,7 +5600,7 @@
         <v>82</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>82</v>
@@ -5658,14 +5611,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5684,16 +5637,16 @@
         <v>82</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>117</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>119</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5731,19 +5684,19 @@
         <v>82</v>
       </c>
       <c r="AB28" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE28" t="s" s="2">
         <v>120</v>
       </c>
-      <c r="AC28" t="s" s="2">
+      <c r="AF28" t="s" s="2">
         <v>121</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5752,10 +5705,10 @@
         <v>81</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>82</v>
@@ -5767,7 +5720,7 @@
         <v>82</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>82</v>
@@ -5778,10 +5731,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5804,19 +5757,19 @@
         <v>94</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5865,7 +5818,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5874,11 +5827,11 @@
         <v>81</v>
       </c>
       <c r="AI29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ29" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK29" t="s" s="2">
         <v>82</v>
       </c>
@@ -5886,10 +5839,10 @@
         <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
@@ -5900,10 +5853,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5926,13 +5879,13 @@
         <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>109</v>
-      </c>
-      <c r="L30" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>111</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5983,7 +5936,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -6007,7 +5960,7 @@
         <v>82</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
@@ -6018,14 +5971,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -6044,16 +5997,16 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>117</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>119</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6091,19 +6044,19 @@
         <v>82</v>
       </c>
       <c r="AB31" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE31" t="s" s="2">
         <v>120</v>
       </c>
-      <c r="AC31" t="s" s="2">
+      <c r="AF31" t="s" s="2">
         <v>121</v>
-      </c>
-      <c r="AD31" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE31" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -6112,10 +6065,10 @@
         <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>82</v>
@@ -6127,7 +6080,7 @@
         <v>82</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -6138,10 +6091,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6164,26 +6117,26 @@
         <v>94</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>82</v>
@@ -6225,7 +6178,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -6234,11 +6187,11 @@
         <v>93</v>
       </c>
       <c r="AI32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ32" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK32" t="s" s="2">
         <v>82</v>
       </c>
@@ -6246,10 +6199,10 @@
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
@@ -6260,10 +6213,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6286,16 +6239,16 @@
         <v>94</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6345,7 +6298,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6354,11 +6307,11 @@
         <v>93</v>
       </c>
       <c r="AI33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ33" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK33" t="s" s="2">
         <v>82</v>
       </c>
@@ -6366,10 +6319,10 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -6380,10 +6333,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6406,26 +6359,24 @@
         <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>309</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>82</v>
@@ -6467,7 +6418,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6476,11 +6427,11 @@
         <v>93</v>
       </c>
       <c r="AI34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ34" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK34" t="s" s="2">
         <v>82</v>
       </c>
@@ -6488,10 +6439,10 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -6502,10 +6453,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6528,19 +6479,17 @@
         <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>309</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -6589,7 +6538,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6598,11 +6547,11 @@
         <v>93</v>
       </c>
       <c r="AI35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ35" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK35" t="s" s="2">
         <v>82</v>
       </c>
@@ -6610,10 +6559,10 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6624,10 +6573,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6650,19 +6599,19 @@
         <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6711,7 +6660,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6720,11 +6669,11 @@
         <v>93</v>
       </c>
       <c r="AI36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ36" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK36" t="s" s="2">
         <v>82</v>
       </c>
@@ -6732,10 +6681,10 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6746,10 +6695,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6772,19 +6721,19 @@
         <v>94</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6833,7 +6782,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6842,11 +6791,11 @@
         <v>93</v>
       </c>
       <c r="AI37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ37" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK37" t="s" s="2">
         <v>82</v>
       </c>
@@ -6854,10 +6803,10 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6868,14 +6817,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6894,19 +6843,19 @@
         <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -6931,13 +6880,13 @@
         <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>82</v>
@@ -6955,7 +6904,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>93</v>
@@ -6964,36 +6913,36 @@
         <v>93</v>
       </c>
       <c r="AI38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ38" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK38" t="s" s="2">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>355</v>
+        <v>349</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7016,13 +6965,13 @@
         <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>109</v>
-      </c>
-      <c r="L39" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>111</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -7073,7 +7022,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -7097,7 +7046,7 @@
         <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -7108,14 +7057,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7134,16 +7083,16 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>117</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>119</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7181,19 +7130,19 @@
         <v>82</v>
       </c>
       <c r="AB40" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE40" t="s" s="2">
         <v>120</v>
       </c>
-      <c r="AC40" t="s" s="2">
+      <c r="AF40" t="s" s="2">
         <v>121</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7202,10 +7151,10 @@
         <v>81</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>82</v>
@@ -7217,7 +7166,7 @@
         <v>82</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -7228,10 +7177,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7254,19 +7203,19 @@
         <v>94</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -7303,17 +7252,17 @@
         <v>82</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="AC41" s="2"/>
       <c r="AD41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7322,11 +7271,11 @@
         <v>81</v>
       </c>
       <c r="AI41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ41" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK41" t="s" s="2">
         <v>82</v>
       </c>
@@ -7334,10 +7283,10 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7348,13 +7297,13 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="D42" t="s" s="2">
         <v>82</v>
@@ -7376,19 +7325,19 @@
         <v>94</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -7398,7 +7347,7 @@
         <v>82</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>82</v>
@@ -7437,7 +7386,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7446,11 +7395,11 @@
         <v>81</v>
       </c>
       <c r="AI42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ42" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK42" t="s" s="2">
         <v>82</v>
       </c>
@@ -7458,10 +7407,10 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -7472,10 +7421,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7498,19 +7447,19 @@
         <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7559,7 +7508,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7568,11 +7517,11 @@
         <v>93</v>
       </c>
       <c r="AI43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ43" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK43" t="s" s="2">
         <v>82</v>
       </c>
@@ -7580,10 +7529,10 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7594,10 +7543,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7620,19 +7569,19 @@
         <v>94</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7681,7 +7630,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7690,25 +7639,25 @@
         <v>93</v>
       </c>
       <c r="AI44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ44" t="s" s="2">
-        <v>230</v>
-      </c>
       <c r="AK44" t="s" s="2">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>82</v>
@@ -7716,10 +7665,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7742,16 +7691,16 @@
         <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7801,7 +7750,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7810,11 +7759,11 @@
         <v>81</v>
       </c>
       <c r="AI45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ45" t="s" s="2">
-        <v>230</v>
-      </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
       </c>
@@ -7822,13 +7771,13 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>82</v>
@@ -7836,14 +7785,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7862,19 +7811,19 @@
         <v>94</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -7923,7 +7872,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7932,25 +7881,25 @@
         <v>93</v>
       </c>
       <c r="AI46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ46" t="s" s="2">
-        <v>230</v>
-      </c>
       <c r="AK46" t="s" s="2">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>82</v>
@@ -7958,14 +7907,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7984,19 +7933,19 @@
         <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
@@ -8045,7 +7994,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -8054,25 +8003,25 @@
         <v>93</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>82</v>
@@ -8080,10 +8029,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8106,16 +8055,16 @@
         <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8165,7 +8114,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8174,11 +8123,11 @@
         <v>93</v>
       </c>
       <c r="AI48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ48" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK48" t="s" s="2">
         <v>82</v>
       </c>
@@ -8186,13 +8135,13 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>82</v>
@@ -8200,10 +8149,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8226,19 +8175,17 @@
         <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>228</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -8287,7 +8234,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8296,25 +8243,25 @@
         <v>81</v>
       </c>
       <c r="AI49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ49" t="s" s="2">
-        <v>230</v>
-      </c>
       <c r="AK49" t="s" s="2">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
@@ -8322,10 +8269,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8348,19 +8295,19 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -8397,17 +8344,17 @@
         <v>82</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="AC50" s="2"/>
       <c r="AD50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8416,36 +8363,36 @@
         <v>93</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>430</v>
+        <v>424</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8468,13 +8415,13 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>109</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>111</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8525,7 +8472,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8549,7 +8496,7 @@
         <v>82</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8560,14 +8507,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8586,16 +8533,16 @@
         <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>117</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>119</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8633,19 +8580,19 @@
         <v>82</v>
       </c>
       <c r="AB52" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE52" t="s" s="2">
         <v>120</v>
       </c>
-      <c r="AC52" t="s" s="2">
+      <c r="AF52" t="s" s="2">
         <v>121</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8654,10 +8601,10 @@
         <v>81</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>82</v>
@@ -8669,7 +8616,7 @@
         <v>82</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8680,10 +8627,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8706,19 +8653,19 @@
         <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8767,7 +8714,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8776,11 +8723,11 @@
         <v>93</v>
       </c>
       <c r="AI53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ53" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK53" t="s" s="2">
         <v>82</v>
       </c>
@@ -8788,10 +8735,10 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8802,10 +8749,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8828,70 +8775,68 @@
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="P54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q54" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="R54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF54" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="P54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q54" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="R54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X54" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="Z54" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8900,11 +8845,11 @@
         <v>93</v>
       </c>
       <c r="AI54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ54" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK54" t="s" s="2">
         <v>82</v>
       </c>
@@ -8912,10 +8857,10 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8926,10 +8871,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8952,19 +8897,17 @@
         <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>309</v>
-      </c>
+        <v>448</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8974,7 +8917,7 @@
         <v>82</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="T55" t="s" s="2">
         <v>82</v>
@@ -9013,7 +8956,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -9022,11 +8965,11 @@
         <v>93</v>
       </c>
       <c r="AI55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ55" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK55" t="s" s="2">
         <v>82</v>
       </c>
@@ -9034,10 +8977,10 @@
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -9048,10 +8991,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9074,19 +9017,17 @@
         <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>463</v>
-      </c>
+        <v>456</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -9096,7 +9037,7 @@
         <v>82</v>
       </c>
       <c r="S56" t="s" s="2">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="T56" t="s" s="2">
         <v>82</v>
@@ -9135,7 +9076,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9144,10 +9085,10 @@
         <v>93</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>82</v>
@@ -9156,10 +9097,10 @@
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -9170,10 +9111,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9196,19 +9137,19 @@
         <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -9257,7 +9198,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9266,11 +9207,11 @@
         <v>93</v>
       </c>
       <c r="AI57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ57" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK57" t="s" s="2">
         <v>82</v>
       </c>
@@ -9278,10 +9219,10 @@
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -9292,10 +9233,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9318,19 +9259,19 @@
         <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9355,13 +9296,13 @@
         <v>82</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>82</v>
@@ -9379,7 +9320,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9388,10 +9329,10 @@
         <v>93</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>82</v>
@@ -9400,10 +9341,10 @@
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>107</v>
+        <v>192</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9414,14 +9355,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9440,19 +9381,19 @@
         <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9477,13 +9418,13 @@
         <v>82</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>491</v>
+        <v>484</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>82</v>
@@ -9501,7 +9442,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9510,36 +9451,36 @@
         <v>81</v>
       </c>
       <c r="AI59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ59" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>496</v>
+        <v>489</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9562,19 +9503,19 @@
         <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9623,7 +9564,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9632,11 +9573,11 @@
         <v>81</v>
       </c>
       <c r="AI60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ60" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK60" t="s" s="2">
         <v>82</v>
       </c>
@@ -9644,10 +9585,10 @@
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9658,10 +9599,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9684,16 +9625,16 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9719,13 +9660,13 @@
         <v>82</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9743,7 +9684,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9752,36 +9693,36 @@
         <v>93</v>
       </c>
       <c r="AI61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ61" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>514</v>
+        <v>507</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9804,19 +9745,19 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -9841,13 +9782,13 @@
         <v>82</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>82</v>
@@ -9865,7 +9806,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9874,11 +9815,11 @@
         <v>93</v>
       </c>
       <c r="AI62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ62" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK62" t="s" s="2">
         <v>82</v>
       </c>
@@ -9886,10 +9827,10 @@
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
@@ -9900,10 +9841,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9926,16 +9867,16 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9985,7 +9926,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9994,36 +9935,36 @@
         <v>93</v>
       </c>
       <c r="AI63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ63" t="s" s="2">
-        <v>230</v>
-      </c>
       <c r="AK63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>532</v>
+        <v>525</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10046,16 +9987,16 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10105,7 +10046,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10114,36 +10055,36 @@
         <v>93</v>
       </c>
       <c r="AI64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ64" t="s" s="2">
-        <v>230</v>
-      </c>
       <c r="AK64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>538</v>
+        <v>531</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>539</v>
+        <v>532</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>541</v>
+        <v>534</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10166,19 +10107,19 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>547</v>
+        <v>540</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>82</v>
@@ -10227,7 +10168,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10236,10 +10177,10 @@
         <v>81</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>82</v>
@@ -10248,10 +10189,10 @@
         <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -10262,10 +10203,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10288,13 +10229,13 @@
         <v>82</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>109</v>
-      </c>
-      <c r="L66" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>111</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10345,7 +10286,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10369,7 +10310,7 @@
         <v>82</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
@@ -10380,14 +10321,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10406,16 +10347,16 @@
         <v>82</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="L67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>117</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>119</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10453,19 +10394,19 @@
         <v>82</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AC67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF67" t="s" s="2">
         <v>121</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10474,10 +10415,10 @@
         <v>81</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>82</v>
@@ -10489,7 +10430,7 @@
         <v>82</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10500,14 +10441,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10526,19 +10467,19 @@
         <v>94</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
@@ -10587,7 +10528,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10596,10 +10537,10 @@
         <v>81</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>82</v>
@@ -10611,7 +10552,7 @@
         <v>82</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>107</v>
+        <v>192</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10622,10 +10563,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10648,17 +10589,15 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>559</v>
+        <v>552</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>562</v>
-      </c>
+        <v>554</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>82</v>
@@ -10707,7 +10646,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10716,10 +10655,10 @@
         <v>93</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>564</v>
+        <v>105</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>82</v>
@@ -10728,10 +10667,10 @@
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>565</v>
+        <v>556</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>566</v>
+        <v>557</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10742,10 +10681,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>567</v>
+        <v>558</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>567</v>
+        <v>558</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10768,17 +10707,15 @@
         <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="L70" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="L70" t="s" s="2">
-        <v>568</v>
-      </c>
       <c r="M70" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>562</v>
-      </c>
+        <v>560</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>82</v>
@@ -10827,7 +10764,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>567</v>
+        <v>558</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10836,10 +10773,10 @@
         <v>93</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>564</v>
+        <v>105</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>82</v>
@@ -10848,10 +10785,10 @@
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>565</v>
+        <v>556</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>570</v>
+        <v>561</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
@@ -10862,10 +10799,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>571</v>
+        <v>562</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>571</v>
+        <v>562</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10888,19 +10825,19 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>572</v>
+        <v>563</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>573</v>
+        <v>564</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>575</v>
+        <v>566</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>82</v>
@@ -10925,13 +10862,13 @@
         <v>82</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>576</v>
+        <v>567</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>577</v>
+        <v>568</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>82</v>
@@ -10949,7 +10886,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>571</v>
+        <v>562</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10958,22 +10895,22 @@
         <v>93</v>
       </c>
       <c r="AI71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ71" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>578</v>
+        <v>569</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -10984,10 +10921,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>580</v>
+        <v>571</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>580</v>
+        <v>571</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11010,19 +10947,19 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>581</v>
+        <v>572</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>583</v>
+        <v>574</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>584</v>
+        <v>575</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>82</v>
@@ -11047,13 +10984,13 @@
         <v>82</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>586</v>
+        <v>577</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>82</v>
@@ -11071,7 +11008,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>580</v>
+        <v>571</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -11080,22 +11017,22 @@
         <v>81</v>
       </c>
       <c r="AI72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ72" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>578</v>
+        <v>569</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
@@ -11106,10 +11043,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11132,19 +11069,17 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>588</v>
+        <v>579</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>589</v>
+        <v>580</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>591</v>
-      </c>
+        <v>581</v>
+      </c>
+      <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>592</v>
+        <v>582</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>82</v>
@@ -11193,7 +11128,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11202,11 +11137,11 @@
         <v>93</v>
       </c>
       <c r="AI73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ73" t="s" s="2">
-        <v>593</v>
-      </c>
       <c r="AK73" t="s" s="2">
         <v>82</v>
       </c>
@@ -11214,10 +11149,10 @@
         <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>594</v>
+        <v>82</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>595</v>
+        <v>583</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
@@ -11228,10 +11163,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>596</v>
+        <v>584</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>596</v>
+        <v>584</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11254,17 +11189,15 @@
         <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>597</v>
+        <v>585</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>309</v>
-      </c>
+        <v>586</v>
+      </c>
+      <c r="N74" s="2"/>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>82</v>
@@ -11313,7 +11246,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>596</v>
+        <v>584</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11322,11 +11255,11 @@
         <v>93</v>
       </c>
       <c r="AI74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ74" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK74" t="s" s="2">
         <v>82</v>
       </c>
@@ -11334,10 +11267,10 @@
         <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>565</v>
+        <v>556</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>599</v>
+        <v>587</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -11348,10 +11281,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11374,16 +11307,16 @@
         <v>94</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>601</v>
+        <v>589</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>602</v>
+        <v>590</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>603</v>
+        <v>591</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11433,7 +11366,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11442,11 +11375,11 @@
         <v>81</v>
       </c>
       <c r="AI75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ75" t="s" s="2">
-        <v>230</v>
-      </c>
       <c r="AK75" t="s" s="2">
         <v>82</v>
       </c>
@@ -11454,10 +11387,10 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>605</v>
+        <v>593</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>606</v>
+        <v>594</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11468,10 +11401,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>607</v>
+        <v>595</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>607</v>
+        <v>595</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11494,16 +11427,16 @@
         <v>94</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>608</v>
+        <v>596</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>609</v>
+        <v>597</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>610</v>
+        <v>598</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>611</v>
+        <v>599</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11553,7 +11486,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>607</v>
+        <v>595</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11562,11 +11495,11 @@
         <v>81</v>
       </c>
       <c r="AI76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ76" t="s" s="2">
-        <v>230</v>
-      </c>
       <c r="AK76" t="s" s="2">
         <v>82</v>
       </c>
@@ -11574,10 +11507,10 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>605</v>
+        <v>593</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>612</v>
+        <v>600</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
@@ -11588,10 +11521,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>613</v>
+        <v>601</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>613</v>
+        <v>601</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11614,19 +11547,19 @@
         <v>94</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>614</v>
+        <v>602</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>614</v>
+        <v>602</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>615</v>
+        <v>603</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>616</v>
+        <v>604</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>82</v>
@@ -11675,7 +11608,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>613</v>
+        <v>601</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11684,10 +11617,10 @@
         <v>81</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>82</v>
@@ -11696,10 +11629,10 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>618</v>
+        <v>606</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>619</v>
+        <v>607</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
@@ -11710,10 +11643,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>620</v>
+        <v>608</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>620</v>
+        <v>608</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11736,13 +11669,13 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>109</v>
-      </c>
-      <c r="L78" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>111</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11793,7 +11726,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11817,7 +11750,7 @@
         <v>82</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
@@ -11828,14 +11761,14 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>621</v>
+        <v>609</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>621</v>
+        <v>609</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -11854,16 +11787,16 @@
         <v>82</v>
       </c>
       <c r="K79" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="L79" t="s" s="2">
+      <c r="N79" t="s" s="2">
         <v>117</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>119</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11901,19 +11834,19 @@
         <v>82</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AC79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF79" t="s" s="2">
         <v>121</v>
-      </c>
-      <c r="AD79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE79" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AF79" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11922,10 +11855,10 @@
         <v>81</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>82</v>
@@ -11937,7 +11870,7 @@
         <v>82</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
@@ -11948,14 +11881,14 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>622</v>
+        <v>610</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>622</v>
+        <v>610</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -11974,19 +11907,19 @@
         <v>94</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>82</v>
@@ -12035,7 +11968,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -12044,10 +11977,10 @@
         <v>81</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>82</v>
@@ -12059,7 +11992,7 @@
         <v>82</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>107</v>
+        <v>192</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
@@ -12070,10 +12003,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>623</v>
+        <v>611</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>623</v>
+        <v>611</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12096,19 +12029,19 @@
         <v>94</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>626</v>
+        <v>614</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>627</v>
+        <v>615</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>82</v>
@@ -12133,13 +12066,13 @@
         <v>82</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>82</v>
@@ -12157,7 +12090,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>623</v>
+        <v>611</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>93</v>
@@ -12166,25 +12099,25 @@
         <v>93</v>
       </c>
       <c r="AI81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ81" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>628</v>
+        <v>616</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="AP81" t="s" s="2">
         <v>82</v>
@@ -12192,10 +12125,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>629</v>
+        <v>617</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>629</v>
+        <v>617</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12218,19 +12151,19 @@
         <v>94</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>630</v>
+        <v>618</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>631</v>
+        <v>619</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>633</v>
+        <v>621</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>82</v>
@@ -12255,13 +12188,13 @@
         <v>82</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>634</v>
+        <v>622</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>635</v>
+        <v>623</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>82</v>
@@ -12279,7 +12212,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>629</v>
+        <v>617</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12288,36 +12221,36 @@
         <v>93</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>636</v>
+        <v>624</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>637</v>
+        <v>625</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>430</v>
+        <v>424</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>638</v>
+        <v>626</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>638</v>
+        <v>626</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12340,19 +12273,19 @@
         <v>82</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>639</v>
+        <v>627</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>640</v>
+        <v>628</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>641</v>
+        <v>629</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>82</v>
@@ -12377,13 +12310,13 @@
         <v>82</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>82</v>
@@ -12401,7 +12334,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>638</v>
+        <v>626</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12410,10 +12343,10 @@
         <v>93</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>642</v>
+        <v>630</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>82</v>
@@ -12422,10 +12355,10 @@
         <v>82</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>107</v>
+        <v>192</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
@@ -12436,14 +12369,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>643</v>
+        <v>631</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>643</v>
+        <v>631</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -12462,19 +12395,19 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>82</v>
@@ -12499,13 +12432,13 @@
         <v>82</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>491</v>
+        <v>484</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>82</v>
@@ -12523,7 +12456,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>643</v>
+        <v>631</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12532,36 +12465,36 @@
         <v>81</v>
       </c>
       <c r="AI84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ84" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>496</v>
+        <v>489</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>644</v>
+        <v>632</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>644</v>
+        <v>632</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12587,16 +12520,16 @@
         <v>83</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>645</v>
+        <v>633</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>646</v>
+        <v>634</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>547</v>
+        <v>540</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>82</v>
@@ -12645,7 +12578,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>644</v>
+        <v>632</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12657,7 +12590,7 @@
         <v>82</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>82</v>
@@ -12666,10 +12599,10 @@
         <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-04T08:19:08+00:00</t>
+    <t>2025-03-27T13:15:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T13:15:18+00:00</t>
+    <t>2025-03-27T14:27:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T14:27:05+00:00</t>
+    <t>2025-03-27T15:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T15:41:15+00:00</t>
+    <t>2025-03-27T15:45:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T15:45:03+00:00</t>
+    <t>2025-03-27T15:47:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T15:47:29+00:00</t>
+    <t>2025-03-31T07:44:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T07:44:46+00:00</t>
+    <t>2025-03-31T07:48:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T07:48:14+00:00</t>
+    <t>2025-03-31T07:48:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T07:48:39+00:00</t>
+    <t>2025-03-31T11:47:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T11:47:14+00:00</t>
+    <t>2025-03-31T11:46:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T11:46:38+00:00</t>
+    <t>2025-03-31T14:05:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T14:05:37+00:00</t>
+    <t>2025-03-31T15:50:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T15:50:51+00:00</t>
+    <t>2025-03-31T15:55:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T15:55:12+00:00</t>
+    <t>2025-03-31T16:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:04:27+00:00</t>
+    <t>2025-03-31T16:16:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:16:40+00:00</t>
+    <t>2025-03-31T16:26:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:26:20+00:00</t>
+    <t>2025-03-31T16:37:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:37:23+00:00</t>
+    <t>2025-04-01T07:11:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-01T07:11:22+00:00</t>
+    <t>2025-04-01T07:12:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-01T07:12:21+00:00</t>
+    <t>2025-04-01T07:12:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-02T12:26:08+00:00</t>
+    <t>2025-07-07T09:50:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T09:50:30+00:00</t>
+    <t>2025-12-23T16:18:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -456,7 +456,7 @@
     <t>Observation.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -494,7 +494,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -518,7 +518,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -561,7 +561,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -718,7 +718,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -747,7 +747,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Immunization|4.0.1|ImagingStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -827,7 +827,7 @@
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t>value:coding.code}
@@ -1082,7 +1082,7 @@
     <t>This identifies the vital sign result type.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1165,7 +1165,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1497,7 +1497,7 @@
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t>obs-6
@@ -1529,7 +1529,7 @@
     <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1585,7 +1585,7 @@
     <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1618,7 +1618,7 @@
     <t>Methods for simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1630,7 +1630,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -1739,7 +1739,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1789,7 +1789,7 @@
     <t>Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1822,7 +1822,7 @@
     <t>Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1859,7 +1859,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(QuestionnaireResponse|MolecularSequence|vitalsigns)
+    <t xml:space="preserve">Reference(QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1|vitalsigns|4.0.1)
 </t>
   </si>
   <si>
@@ -1881,7 +1881,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|MolecularSequence|vitalsigns)
+    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1|vitalsigns|4.0.1)
 </t>
   </si>
   <si>
@@ -2347,7 +2347,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="43.5859375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="47.9921875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -5127,7 +5127,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
         <v>240</v>
       </c>
@@ -5367,7 +5367,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>263</v>
       </c>
@@ -5729,7 +5729,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
         <v>269</v>
       </c>
@@ -6089,7 +6089,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>282</v>
       </c>
@@ -6331,7 +6331,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
         <v>300</v>
       </c>
@@ -6815,7 +6815,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
         <v>336</v>
       </c>
@@ -7541,7 +7541,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
         <v>358</v>
       </c>
@@ -7905,7 +7905,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
         <v>385</v>
       </c>
@@ -9231,7 +9231,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
         <v>469</v>
       </c>
@@ -9959,7 +9959,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
         <v>526</v>
       </c>
@@ -11519,7 +11519,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="77" hidden="true">
+    <row r="77">
       <c r="A77" t="s" s="2">
         <v>601</v>
       </c>
@@ -12001,7 +12001,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="81" hidden="true">
+    <row r="81">
       <c r="A81" t="s" s="2">
         <v>611</v>
       </c>
@@ -12123,7 +12123,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="82" hidden="true">
+    <row r="82">
       <c r="A82" t="s" s="2">
         <v>617</v>
       </c>
@@ -12245,7 +12245,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="83" hidden="true">
+    <row r="83">
       <c r="A83" t="s" s="2">
         <v>626</v>
       </c>
@@ -12613,12 +12613,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AP85">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-23T16:18:55+00:00</t>
+    <t>2026-01-06T09:57:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-06T09:57:05+00:00</t>
+    <t>2026-01-06T10:01:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$95</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3290" uniqueCount="635">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3675" uniqueCount="670">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-06T10:01:17+00:00</t>
+    <t>2026-01-19T08:51:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/vitalsigns</t>
+    <t>http://hl7.org/fhir/StructureDefinition/headcircum</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -272,10 +272,10 @@
 </t>
   </si>
   <si>
-    <t>FHIR Vital Signs Profile</t>
-  </si>
-  <si>
-    <t>The FHIR Vitals Signs profile sets minimum expectations for the Observation Resource to record, search and fetch the vital signs associated with a patient.</t>
+    <t>FHIR Head Circumference Profile</t>
+  </si>
+  <si>
+    <t>This profile defines  how to represent Head Circumference observations in FHIR using a standard LOINC code and UCUM units of measure.</t>
   </si>
   <si>
     <t>Used for simple observations such as device measurements, laboratory atomic results, vital signs, height, weight, smoking status, comments, etc.  Other resources are used to provide context for observations such as laboratory reports, etc.</t>
@@ -439,8 +439,7 @@
 </t>
   </si>
   <si>
-    <t>Uri identifiant les systèmes tiers ayant envoyé la ressource.
-L’uri est sous la forme d’un oid : « urn:oid:xx.xx.xx »</t>
+    <t>Uri identifiant les systèmes tiers ayant envoyé la ressource. L’uri est sous la forme d’une oid : « urn:oid:xx.xx.xx »</t>
   </si>
   <si>
     <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
@@ -644,7 +643,7 @@
     <t>Other information that may be relevant to this event.</t>
   </si>
   <si>
-    <t>Other resources *from the patient record* that may be relevant to the event.  The information from these resources was either used to create the instance or is provided to help with its interpretation.  This extension **should not** be used if more specific  inline elements  or extensions are available.  For example, use `Observation.hasMember`  instead of supportingInformation for  representing the members of an Observation panel.</t>
+    <t>Autres ressources pertinentes *du dossier patient*</t>
   </si>
   <si>
     <t>Observation.extension:MesReasonForMeasurement</t>
@@ -660,13 +659,30 @@
     <t>Motif de la mesure</t>
   </si>
   <si>
-    <t>Extension du Motif de la mesure, exprimé en texte libre.</t>
+    <t>Motif de la mesure
+Texte libre (ex. diabète, surpoids, hypercholestérolémie, risque cardiovasculaire, suivi, ...)</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
+    <t>Observation.extension:MesOriginOfData</t>
+  </si>
+  <si>
+    <t>MesOriginOfData</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-origin-of-data}
+</t>
+  </si>
+  <si>
+    <t>Origine de la donnée</t>
+  </si>
+  <si>
+    <t>Extension pour tracer l'origine de la donnée issue d'un compte rendu de biologie (CR-Bio).</t>
+  </si>
+  <si>
     <t>Observation.modifierExtension</t>
   </si>
   <si>
@@ -1063,17 +1079,17 @@
     <t>Observation.code</t>
   </si>
   <si>
-    <t xml:space="preserve">Name
-</t>
-  </si>
-  <si>
-    <t>Coded Responses from C-CDA Vital Sign Results</t>
-  </si>
-  <si>
-    <t>Coded Responses from C-CDA Vital Sign Results.</t>
-  </si>
-  <si>
-    <t>*All* code-value and, if present, component.code-component.value pairs need to be taken into account to correctly understand the meaning of the observation.</t>
+    <t>Name
+Test</t>
+  </si>
+  <si>
+    <t>Head Circumference</t>
+  </si>
+  <si>
+    <t>Head Circumference.</t>
+  </si>
+  <si>
+    <t>additional codes that translate or map to this code are allowed.  For example a more granular LOINC code or code that is used locally in a system.</t>
   </si>
   <si>
     <t>5. SHALL contain exactly one [1..1] code, where the @code SHOULD be selected from ValueSet HITSP Vital Sign Result Type 2.16.840.1.113883.3.88.12.80.62 DYNAMIC (CONF:7301).</t>
@@ -1110,10 +1126,67 @@
   </si>
   <si>
     <t>Observation.code.coding</t>
+  </si>
+  <si>
+    <t>2</t>
   </si>
   <si>
     <t>value:code}
 value:system}</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:HeadCircumCode</t>
+  </si>
+  <si>
+    <t>HeadCircumCode</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:HeadCircumCode.id</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.id</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:HeadCircumCode.extension</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.extension</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:HeadCircumCode.system</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.system</t>
+  </si>
+  <si>
+    <t>http://loinc.org</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:HeadCircumCode.version</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.version</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:HeadCircumCode.code</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.code</t>
+  </si>
+  <si>
+    <t>9843-4</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:HeadCircumCode.display</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.display</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:HeadCircumCode.userSelected</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.userSelected</t>
   </si>
   <si>
     <t>Observation.code.coding:headCircumCode</t>
@@ -1283,7 +1356,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CareTeam|RelatedPerson|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
+    <t xml:space="preserve">Reference(CareTeam|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
 </t>
   </si>
   <si>
@@ -1328,6 +1401,9 @@
 </t>
   </si>
   <si>
+    <t>closed</t>
+  </si>
+  <si>
     <t>obs-7
 vs-2</t>
   </si>
@@ -1344,10 +1420,25 @@
     <t>363714003 |Interprets|</t>
   </si>
   <si>
+    <t>Observation.value[x]:valueQuantity</t>
+  </si>
+  <si>
+    <t>valueQuantity</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueQuantity.id</t>
+  </si>
+  <si>
     <t>Observation.value[x].id</t>
   </si>
   <si>
+    <t>Observation.value[x]:valueQuantity.extension</t>
+  </si>
+  <si>
     <t>Observation.value[x].extension</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueQuantity.value</t>
   </si>
   <si>
     <t>Observation.value[x].value</t>
@@ -1378,6 +1469,9 @@
     <t>PQ.value, CO.value, MO.value, IVL.high or IVL.low depending on the value</t>
   </si>
   <si>
+    <t>Observation.value[x]:valueQuantity.comparator</t>
+  </si>
+  <si>
     <t>Observation.value[x].comparator</t>
   </si>
   <si>
@@ -1408,6 +1502,9 @@
     <t>IVL properties</t>
   </si>
   <si>
+    <t>Observation.value[x]:valueQuantity.unit</t>
+  </si>
+  <si>
     <t>Observation.value[x].unit</t>
   </si>
   <si>
@@ -1430,6 +1527,9 @@
   </si>
   <si>
     <t>PQ.unit</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueQuantity.system</t>
   </si>
   <si>
     <t>Observation.value[x].system</t>
@@ -1457,19 +1557,25 @@
     <t>CO.codeSystem, PQ.translation.codeSystem</t>
   </si>
   <si>
+    <t>Observation.value[x]:valueQuantity.code</t>
+  </si>
+  <si>
     <t>Observation.value[x].code</t>
   </si>
   <si>
-    <t>Coded form of the unit</t>
-  </si>
-  <si>
-    <t>A computer processable form of the unit in some unit representation system.</t>
+    <t>Coded responses from the common UCUM units for vital signs value set.</t>
   </si>
   <si>
     <t>The preferred system is UCUM, but SNOMED CT can also be used (for customary units) or ISO 4217 for currency.  The context of use may additionally require a code from a particular system.</t>
   </si>
   <si>
     <t>Need a computable form of the unit that is fixed across all forms. UCUM provides this for quantities, but SNOMED CT provides many units of interest.</t>
+  </si>
+  <si>
+    <t>Common UCUM units for body length measures such as Body Height and Head Circumference.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/ucum-bodylength|4.0.1</t>
   </si>
   <si>
     <t>Quantity.code</t>
@@ -2319,10 +2425,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP85"/>
+  <dimension ref="A1:AP95"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="41.46484375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="45.484375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="23.171875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
@@ -2332,7 +2438,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="191.30859375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="232.12890625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -4650,43 +4756,41 @@
         <v>208</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="C20" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>209</v>
+      </c>
       <c r="D20" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>114</v>
+        <v>210</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>211</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>82</v>
       </c>
@@ -4734,7 +4838,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4743,7 +4847,7 @@
         <v>81</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>82</v>
+        <v>207</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>122</v>
@@ -4758,7 +4862,7 @@
         <v>82</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>192</v>
+        <v>82</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>82</v>
@@ -4776,7 +4880,7 @@
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4789,23 +4893,25 @@
         <v>82</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O21" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="N21" s="2"/>
-      <c r="O21" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>82</v>
@@ -4854,7 +4960,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4866,22 +4972,22 @@
         <v>82</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>218</v>
+        <v>82</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>219</v>
+        <v>82</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>220</v>
+        <v>192</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>221</v>
+        <v>82</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>82</v>
@@ -4889,14 +4995,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>223</v>
+        <v>82</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4915,17 +5021,17 @@
         <v>94</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>82</v>
@@ -4974,7 +5080,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4989,19 +5095,19 @@
         <v>105</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>82</v>
+        <v>226</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>82</v>
@@ -5009,14 +5115,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -5035,18 +5141,18 @@
         <v>94</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="O23" s="2"/>
+        <v>231</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>82</v>
       </c>
@@ -5094,7 +5200,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -5109,16 +5215,16 @@
         <v>105</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>82</v>
@@ -5127,48 +5233,46 @@
         <v>82</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>82</v>
+        <v>237</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>169</v>
+        <v>238</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="N24" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="M24" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>244</v>
-      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>82</v>
       </c>
@@ -5192,11 +5296,13 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="Y24" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z24" t="s" s="2">
-        <v>246</v>
+        <v>82</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
@@ -5214,13 +5320,13 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>82</v>
@@ -5229,30 +5335,30 @@
         <v>105</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>248</v>
+        <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>251</v>
+        <v>82</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5263,31 +5369,31 @@
         <v>93</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>94</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>253</v>
+        <v>169</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -5312,35 +5418,35 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>258</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="AC25" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>82</v>
@@ -5349,34 +5455,32 @@
         <v>105</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>82</v>
+        <v>252</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>82</v>
+        <v>253</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>82</v>
+        <v>254</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="C26" t="s" s="2">
-        <v>264</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
         <v>82</v>
       </c>
@@ -5385,7 +5489,7 @@
         <v>93</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>94</v>
@@ -5397,19 +5501,19 @@
         <v>82</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -5437,28 +5541,26 @@
         <v>173</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="AC26" s="2"/>
       <c r="AD26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5482,35 +5584,37 @@
         <v>82</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="C27" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>269</v>
+      </c>
       <c r="D27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>82</v>
@@ -5519,16 +5623,20 @@
         <v>82</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>107</v>
+        <v>258</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>108</v>
+        <v>259</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
+        <v>260</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>262</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
       </c>
@@ -5552,13 +5660,13 @@
         <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>82</v>
+        <v>173</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>82</v>
+        <v>263</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>82</v>
+        <v>264</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
@@ -5576,19 +5684,19 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>110</v>
+        <v>257</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>82</v>
@@ -5600,10 +5708,10 @@
         <v>82</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>111</v>
+        <v>266</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>82</v>
+        <v>267</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>82</v>
@@ -5611,21 +5719,21 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>82</v>
@@ -5637,17 +5745,15 @@
         <v>82</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5684,31 +5790,31 @@
         <v>82</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>82</v>
@@ -5729,48 +5835,46 @@
         <v>82</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>147</v>
+        <v>114</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>271</v>
+        <v>115</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>272</v>
+        <v>116</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>82</v>
       </c>
@@ -5806,19 +5910,19 @@
         <v>82</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>275</v>
+        <v>121</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5830,7 +5934,7 @@
         <v>82</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>82</v>
@@ -5839,10 +5943,10 @@
         <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>276</v>
+        <v>82</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>277</v>
+        <v>111</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
@@ -5851,12 +5955,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5864,31 +5968,35 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>107</v>
+        <v>147</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>108</v>
+        <v>276</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
+        <v>277</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>279</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
       </c>
@@ -5936,19 +6044,19 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>110</v>
+        <v>280</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>82</v>
@@ -5957,10 +6065,10 @@
         <v>82</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>82</v>
+        <v>281</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>111</v>
+        <v>282</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
@@ -5971,21 +6079,21 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>82</v>
@@ -5997,17 +6105,15 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -6044,31 +6150,31 @@
         <v>82</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>82</v>
@@ -6089,134 +6195,132 @@
         <v>82</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>284</v>
+        <v>115</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>285</v>
+        <v>116</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>287</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AF32" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN32" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AO32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP32" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="B33" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="S32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="AG32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH32" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ32" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP32" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="33" hidden="true">
-      <c r="A33" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6224,13 +6328,13 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>82</v>
@@ -6239,24 +6343,26 @@
         <v>94</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="O33" s="2"/>
+        <v>291</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>292</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>82</v>
+        <v>293</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>82</v>
@@ -6298,7 +6404,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6319,24 +6425,24 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AN33" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AO33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP33" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="34" hidden="true">
+      <c r="A34" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="B34" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP33" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6344,13 +6450,13 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>82</v>
@@ -6359,24 +6465,24 @@
         <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>169</v>
+        <v>107</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" t="s" s="2">
-        <v>304</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>305</v>
+        <v>82</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>82</v>
@@ -6418,7 +6524,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6439,10 +6545,10 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -6451,12 +6557,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6464,13 +6570,13 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>82</v>
@@ -6479,24 +6585,24 @@
         <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>107</v>
+        <v>169</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>82</v>
+        <v>310</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>82</v>
@@ -6538,7 +6644,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6559,10 +6665,10 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6573,10 +6679,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6599,19 +6705,17 @@
         <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>319</v>
+        <v>107</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>322</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6660,7 +6764,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6681,10 +6785,10 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6695,10 +6799,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6721,19 +6825,19 @@
         <v>94</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>107</v>
+        <v>324</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6782,7 +6886,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6803,10 +6907,10 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6815,26 +6919,26 @@
         <v>82</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>337</v>
+        <v>82</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>82</v>
@@ -6843,19 +6947,19 @@
         <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>253</v>
+        <v>107</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -6880,13 +6984,13 @@
         <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>342</v>
+        <v>82</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>343</v>
+        <v>82</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>82</v>
@@ -6904,10 +7008,10 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>93</v>
@@ -6919,62 +7023,66 @@
         <v>105</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>344</v>
+        <v>82</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>345</v>
+        <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>348</v>
+        <v>82</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>349</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>82</v>
+        <v>342</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>107</v>
+        <v>258</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>108</v>
+        <v>343</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+        <v>344</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>346</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
       </c>
@@ -6998,13 +7106,13 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>82</v>
+        <v>347</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>82</v>
+        <v>348</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -7022,10 +7130,10 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>110</v>
+        <v>341</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>93</v>
@@ -7034,44 +7142,44 @@
         <v>82</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>82</v>
+        <v>349</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>82</v>
+        <v>350</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>82</v>
+        <v>351</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>111</v>
+        <v>352</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>82</v>
+        <v>353</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>82</v>
+        <v>354</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>82</v>
@@ -7083,17 +7191,15 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -7130,31 +7236,31 @@
         <v>82</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>82</v>
@@ -7177,18 +7283,18 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>81</v>
@@ -7200,23 +7306,21 @@
         <v>82</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>147</v>
+        <v>114</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>271</v>
+        <v>115</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>272</v>
+        <v>116</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
@@ -7252,9 +7356,11 @@
         <v>82</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="AC41" s="2"/>
+        <v>118</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>119</v>
+      </c>
       <c r="AD41" t="s" s="2">
         <v>82</v>
       </c>
@@ -7262,7 +7368,7 @@
         <v>120</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>275</v>
+        <v>121</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7274,7 +7380,7 @@
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>82</v>
@@ -7283,10 +7389,10 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>276</v>
+        <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>277</v>
+        <v>111</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7297,23 +7403,21 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="C42" t="s" s="2">
-        <v>355</v>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>93</v>
+        <v>358</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
@@ -7328,16 +7432,16 @@
         <v>147</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -7347,7 +7451,7 @@
         <v>82</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>356</v>
+        <v>82</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>82</v>
@@ -7374,19 +7478,17 @@
         <v>82</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="AC42" s="2"/>
       <c r="AD42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7407,10 +7509,10 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -7421,18 +7523,20 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="C43" s="2"/>
+      <c r="C43" t="s" s="2">
+        <v>361</v>
+      </c>
       <c r="D43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>93</v>
@@ -7447,19 +7551,19 @@
         <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>107</v>
+        <v>147</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>329</v>
+        <v>276</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>330</v>
+        <v>277</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>331</v>
+        <v>278</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>332</v>
+        <v>279</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7508,13 +7612,13 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>333</v>
+        <v>280</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>82</v>
@@ -7529,10 +7633,10 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>334</v>
+        <v>281</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>335</v>
+        <v>282</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7541,12 +7645,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7554,35 +7658,31 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>359</v>
+        <v>107</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>360</v>
+        <v>108</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>363</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>82</v>
       </c>
@@ -7630,7 +7730,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>358</v>
+        <v>110</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7642,22 +7742,22 @@
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>364</v>
+        <v>82</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>365</v>
+        <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>366</v>
+        <v>111</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>367</v>
+        <v>82</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>82</v>
@@ -7665,14 +7765,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7688,19 +7788,19 @@
         <v>82</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>369</v>
+        <v>114</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>370</v>
+        <v>115</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>371</v>
+        <v>116</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>372</v>
+        <v>117</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7738,19 +7838,19 @@
         <v>82</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>368</v>
+        <v>121</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7762,7 +7862,7 @@
         <v>82</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
@@ -7771,13 +7871,13 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>346</v>
+        <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>373</v>
+        <v>111</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>367</v>
+        <v>82</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>82</v>
@@ -7785,18 +7885,18 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>375</v>
+        <v>82</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>93</v>
@@ -7811,26 +7911,26 @@
         <v>94</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>376</v>
+        <v>135</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>377</v>
+        <v>289</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>378</v>
+        <v>290</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>379</v>
+        <v>291</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>380</v>
+        <v>292</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>82</v>
+        <v>368</v>
       </c>
       <c r="S46" t="s" s="2">
         <v>82</v>
@@ -7872,7 +7972,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>374</v>
+        <v>294</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7887,44 +7987,44 @@
         <v>105</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>381</v>
+        <v>82</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>382</v>
+        <v>295</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>383</v>
+        <v>296</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>384</v>
+        <v>82</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>385</v>
+        <v>369</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>385</v>
+        <v>370</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>386</v>
+        <v>82</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>82</v>
@@ -7933,20 +8033,18 @@
         <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>387</v>
+        <v>107</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>388</v>
+        <v>299</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>389</v>
+        <v>300</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>391</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>82</v>
       </c>
@@ -7994,7 +8092,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>385</v>
+        <v>302</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -8003,25 +8101,25 @@
         <v>93</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>392</v>
+        <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>393</v>
+        <v>105</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>394</v>
+        <v>82</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>395</v>
+        <v>303</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>396</v>
+        <v>304</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>397</v>
+        <v>82</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>82</v>
@@ -8029,10 +8127,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>398</v>
+        <v>371</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>398</v>
+        <v>372</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8040,7 +8138,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>93</v>
@@ -8055,24 +8153,24 @@
         <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>129</v>
+        <v>169</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>399</v>
+        <v>307</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="O48" s="2"/>
+        <v>308</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>82</v>
+        <v>373</v>
       </c>
       <c r="S48" t="s" s="2">
         <v>82</v>
@@ -8114,7 +8212,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>398</v>
+        <v>311</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8135,13 +8233,13 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>402</v>
+        <v>312</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>403</v>
+        <v>313</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>404</v>
+        <v>82</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>82</v>
@@ -8149,10 +8247,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>405</v>
+        <v>374</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>405</v>
+        <v>375</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8163,7 +8261,7 @@
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>82</v>
@@ -8175,17 +8273,17 @@
         <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>406</v>
+        <v>107</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>407</v>
+        <v>316</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>408</v>
+        <v>317</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>409</v>
+        <v>318</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -8234,13 +8332,13 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>405</v>
+        <v>319</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>82</v>
@@ -8249,19 +8347,19 @@
         <v>105</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>410</v>
+        <v>82</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>411</v>
+        <v>320</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>412</v>
+        <v>321</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>413</v>
+        <v>82</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
@@ -8269,10 +8367,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>414</v>
+        <v>376</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>414</v>
+        <v>377</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8286,7 +8384,7 @@
         <v>93</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>82</v>
@@ -8295,19 +8393,19 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>415</v>
+        <v>324</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>416</v>
+        <v>325</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>416</v>
+        <v>326</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>417</v>
+        <v>327</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>418</v>
+        <v>328</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -8344,17 +8442,19 @@
         <v>82</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="AC50" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>414</v>
+        <v>329</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8363,7 +8463,7 @@
         <v>93</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>420</v>
+        <v>82</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>105</v>
@@ -8372,35 +8472,37 @@
         <v>82</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>421</v>
+        <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>422</v>
+        <v>330</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>423</v>
+        <v>331</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>424</v>
+        <v>82</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>425</v>
+        <v>378</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="C51" s="2"/>
+        <v>357</v>
+      </c>
+      <c r="C51" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="D51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>93</v>
@@ -8412,19 +8514,23 @@
         <v>82</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>107</v>
+        <v>147</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>108</v>
+        <v>276</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+        <v>277</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>279</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
       </c>
@@ -8433,7 +8539,7 @@
         <v>82</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>82</v>
+        <v>380</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>82</v>
@@ -8472,19 +8578,19 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>110</v>
+        <v>280</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>82</v>
@@ -8493,10 +8599,10 @@
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>82</v>
+        <v>281</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>111</v>
+        <v>282</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8507,21 +8613,21 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>426</v>
+        <v>381</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>426</v>
+        <v>381</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>82</v>
@@ -8530,21 +8636,23 @@
         <v>82</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>115</v>
+        <v>334</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>116</v>
+        <v>335</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O52" s="2"/>
+        <v>336</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>337</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
       </c>
@@ -8580,31 +8688,31 @@
         <v>82</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>121</v>
+        <v>338</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>82</v>
@@ -8613,10 +8721,10 @@
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>82</v>
+        <v>339</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>111</v>
+        <v>340</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8625,12 +8733,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
-        <v>427</v>
+        <v>382</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>427</v>
+        <v>382</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8644,7 +8752,7 @@
         <v>93</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>82</v>
@@ -8653,19 +8761,19 @@
         <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>428</v>
+        <v>383</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>429</v>
+        <v>384</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>430</v>
+        <v>385</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>431</v>
+        <v>386</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>432</v>
+        <v>387</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8714,7 +8822,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>433</v>
+        <v>382</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8729,19 +8837,19 @@
         <v>105</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>82</v>
+        <v>388</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>434</v>
+        <v>389</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>435</v>
+        <v>390</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>82</v>
+        <v>391</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>82</v>
@@ -8749,10 +8857,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>436</v>
+        <v>392</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>436</v>
+        <v>392</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8763,36 +8871,34 @@
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J54" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>169</v>
+        <v>393</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>437</v>
+        <v>394</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" t="s" s="2">
-        <v>439</v>
-      </c>
+        <v>395</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q54" t="s" s="2">
-        <v>440</v>
-      </c>
+      <c r="Q54" s="2"/>
       <c r="R54" t="s" s="2">
         <v>82</v>
       </c>
@@ -8812,13 +8918,13 @@
         <v>82</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>245</v>
+        <v>82</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>441</v>
+        <v>82</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>442</v>
+        <v>82</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>82</v>
@@ -8836,13 +8942,13 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>443</v>
+        <v>392</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>82</v>
@@ -8857,13 +8963,13 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>444</v>
+        <v>351</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>445</v>
+        <v>397</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>82</v>
+        <v>391</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>82</v>
@@ -8871,14 +8977,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>446</v>
+        <v>398</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>446</v>
+        <v>398</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>82</v>
+        <v>399</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8897,17 +9003,19 @@
         <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>107</v>
+        <v>400</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>447</v>
+        <v>401</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>402</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>403</v>
+      </c>
       <c r="O55" t="s" s="2">
-        <v>449</v>
+        <v>404</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8917,7 +9025,7 @@
         <v>82</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>450</v>
+        <v>82</v>
       </c>
       <c r="T55" t="s" s="2">
         <v>82</v>
@@ -8956,7 +9064,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>451</v>
+        <v>398</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8971,44 +9079,44 @@
         <v>105</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>82</v>
+        <v>405</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>452</v>
+        <v>406</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>453</v>
+        <v>407</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>82</v>
+        <v>408</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>454</v>
+        <v>409</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>454</v>
+        <v>409</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>82</v>
+        <v>410</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>82</v>
@@ -9017,17 +9125,19 @@
         <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>135</v>
+        <v>411</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>455</v>
+        <v>412</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>413</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>414</v>
+      </c>
       <c r="O56" t="s" s="2">
-        <v>457</v>
+        <v>415</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -9037,7 +9147,7 @@
         <v>82</v>
       </c>
       <c r="S56" t="s" s="2">
-        <v>458</v>
+        <v>82</v>
       </c>
       <c r="T56" t="s" s="2">
         <v>82</v>
@@ -9076,7 +9186,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>459</v>
+        <v>409</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9085,25 +9195,25 @@
         <v>93</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>460</v>
+        <v>416</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>105</v>
+        <v>417</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>82</v>
+        <v>418</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>452</v>
+        <v>419</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>461</v>
+        <v>420</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>82</v>
+        <v>421</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>82</v>
@@ -9111,10 +9221,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>462</v>
+        <v>422</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>462</v>
+        <v>422</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9122,7 +9232,7 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>93</v>
@@ -9137,20 +9247,18 @@
         <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>169</v>
+        <v>129</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>463</v>
+        <v>423</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>464</v>
+        <v>424</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>466</v>
-      </c>
+        <v>425</v>
+      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>82</v>
       </c>
@@ -9198,7 +9306,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>467</v>
+        <v>422</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9219,24 +9327,24 @@
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>452</v>
+        <v>426</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>468</v>
+        <v>427</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>82</v>
+        <v>428</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>469</v>
+        <v>429</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>469</v>
+        <v>429</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9247,31 +9355,29 @@
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J58" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="I58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J58" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K58" t="s" s="2">
-        <v>253</v>
+        <v>430</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>470</v>
+        <v>431</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>472</v>
-      </c>
+        <v>432</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>473</v>
+        <v>433</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9296,13 +9402,13 @@
         <v>82</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>474</v>
+        <v>82</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>475</v>
+        <v>82</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>82</v>
@@ -9320,34 +9426,34 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>469</v>
+        <v>429</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>476</v>
+        <v>82</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>82</v>
+        <v>434</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>192</v>
+        <v>435</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>477</v>
+        <v>436</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>82</v>
+        <v>437</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>82</v>
@@ -9355,45 +9461,45 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>478</v>
+        <v>438</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>478</v>
+        <v>438</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>479</v>
+        <v>82</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>253</v>
+        <v>439</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>480</v>
+        <v>440</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>481</v>
+        <v>440</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>482</v>
+        <v>441</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>483</v>
+        <v>442</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9418,40 +9524,38 @@
         <v>82</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>484</v>
+        <v>82</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>485</v>
+        <v>82</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>443</v>
+      </c>
+      <c r="AC59" s="2"/>
       <c r="AD59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>82</v>
+        <v>444</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>478</v>
+        <v>438</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>82</v>
+        <v>445</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>105</v>
@@ -9460,29 +9564,31 @@
         <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>486</v>
+        <v>446</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>487</v>
+        <v>447</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>488</v>
+        <v>448</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>489</v>
+        <v>449</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
-        <v>490</v>
+        <v>450</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="C60" s="2"/>
+        <v>438</v>
+      </c>
+      <c r="C60" t="s" s="2">
+        <v>451</v>
+      </c>
       <c r="D60" t="s" s="2">
         <v>82</v>
       </c>
@@ -9491,31 +9597,31 @@
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>491</v>
+        <v>439</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>492</v>
+        <v>440</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>493</v>
+        <v>440</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>494</v>
+        <v>441</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>495</v>
+        <v>442</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9564,16 +9670,16 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>490</v>
+        <v>438</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>82</v>
+        <v>445</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>105</v>
@@ -9582,27 +9688,27 @@
         <v>82</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>82</v>
+        <v>446</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>496</v>
+        <v>447</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>497</v>
+        <v>448</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>82</v>
+        <v>449</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>498</v>
+        <v>452</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>498</v>
+        <v>453</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9625,17 +9731,15 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>253</v>
+        <v>107</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>499</v>
+        <v>108</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>501</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9660,13 +9764,13 @@
         <v>82</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>159</v>
+        <v>82</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>502</v>
+        <v>82</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>503</v>
+        <v>82</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9684,7 +9788,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>498</v>
+        <v>110</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9696,44 +9800,44 @@
         <v>82</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>504</v>
+        <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>505</v>
+        <v>82</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>506</v>
+        <v>111</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>507</v>
+        <v>82</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>508</v>
+        <v>454</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>508</v>
+        <v>455</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>82</v>
@@ -9745,20 +9849,18 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>253</v>
+        <v>114</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>509</v>
+        <v>115</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>510</v>
+        <v>116</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>512</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>82</v>
       </c>
@@ -9782,43 +9884,43 @@
         <v>82</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>159</v>
+        <v>82</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>513</v>
+        <v>82</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>514</v>
+        <v>82</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>508</v>
+        <v>121</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>82</v>
@@ -9827,10 +9929,10 @@
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>515</v>
+        <v>82</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>516</v>
+        <v>111</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
@@ -9839,12 +9941,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
-        <v>517</v>
+        <v>456</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>517</v>
+        <v>457</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9852,33 +9954,35 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>518</v>
+        <v>458</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>519</v>
+        <v>459</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>520</v>
+        <v>460</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="O63" s="2"/>
+        <v>461</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>462</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
       </c>
@@ -9926,7 +10030,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>517</v>
+        <v>463</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9944,27 +10048,27 @@
         <v>82</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>522</v>
+        <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>523</v>
+        <v>464</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>524</v>
+        <v>465</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>525</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>526</v>
+        <v>466</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>526</v>
+        <v>467</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9978,31 +10082,33 @@
         <v>93</v>
       </c>
       <c r="H64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I64" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="I64" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="J64" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>527</v>
+        <v>169</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>528</v>
+        <v>468</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="O64" s="2"/>
+        <v>469</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" t="s" s="2">
+        <v>470</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q64" s="2"/>
+      <c r="Q64" t="s" s="2">
+        <v>471</v>
+      </c>
       <c r="R64" t="s" s="2">
         <v>82</v>
       </c>
@@ -10022,13 +10128,13 @@
         <v>82</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>82</v>
+        <v>250</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>82</v>
+        <v>472</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>82</v>
+        <v>473</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>82</v>
@@ -10046,7 +10152,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>526</v>
+        <v>474</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10064,27 +10170,27 @@
         <v>82</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>531</v>
+        <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>532</v>
+        <v>475</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>533</v>
+        <v>476</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>534</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
-        <v>535</v>
+        <v>477</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>535</v>
+        <v>478</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10092,34 +10198,32 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>536</v>
+        <v>107</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>537</v>
+        <v>479</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>539</v>
-      </c>
+        <v>480</v>
+      </c>
+      <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>540</v>
+        <v>481</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>82</v>
@@ -10129,7 +10233,7 @@
         <v>82</v>
       </c>
       <c r="S65" t="s" s="2">
-        <v>82</v>
+        <v>482</v>
       </c>
       <c r="T65" t="s" s="2">
         <v>82</v>
@@ -10168,19 +10272,19 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>535</v>
+        <v>483</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>541</v>
+        <v>105</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>82</v>
@@ -10189,10 +10293,10 @@
         <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>542</v>
+        <v>484</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>543</v>
+        <v>485</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -10201,12 +10305,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
-        <v>544</v>
+        <v>486</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>544</v>
+        <v>487</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10214,37 +10318,39 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>108</v>
+        <v>488</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>109</v>
+        <v>489</v>
       </c>
       <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
+      <c r="O66" t="s" s="2">
+        <v>490</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q66" s="2"/>
       <c r="R66" t="s" s="2">
-        <v>82</v>
+        <v>491</v>
       </c>
       <c r="S66" t="s" s="2">
         <v>82</v>
@@ -10286,7 +10392,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>110</v>
+        <v>492</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10295,10 +10401,10 @@
         <v>93</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>82</v>
+        <v>493</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>82</v>
@@ -10307,10 +10413,10 @@
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>82</v>
+        <v>484</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>111</v>
+        <v>494</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
@@ -10319,46 +10425,48 @@
         <v>82</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
-        <v>545</v>
+        <v>495</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>545</v>
+        <v>496</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>114</v>
+        <v>169</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>115</v>
+        <v>497</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>116</v>
+        <v>497</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O67" s="2"/>
+        <v>498</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>499</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
       </c>
@@ -10367,7 +10475,7 @@
         <v>82</v>
       </c>
       <c r="S67" t="s" s="2">
-        <v>82</v>
+        <v>482</v>
       </c>
       <c r="T67" t="s" s="2">
         <v>82</v>
@@ -10382,13 +10490,13 @@
         <v>82</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>82</v>
+        <v>250</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>82</v>
+        <v>500</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>82</v>
+        <v>501</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>82</v>
@@ -10406,19 +10514,19 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>121</v>
+        <v>502</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>82</v>
@@ -10427,10 +10535,10 @@
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>82</v>
+        <v>484</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>111</v>
+        <v>503</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10439,47 +10547,47 @@
         <v>82</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
-        <v>546</v>
+        <v>504</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>546</v>
+        <v>504</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>547</v>
+        <v>82</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>114</v>
+        <v>258</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>548</v>
+        <v>505</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>549</v>
+        <v>506</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>117</v>
+        <v>507</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>211</v>
+        <v>508</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
@@ -10504,13 +10612,13 @@
         <v>82</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>82</v>
+        <v>509</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>82</v>
+        <v>510</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>82</v>
@@ -10528,19 +10636,19 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>550</v>
+        <v>504</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>82</v>
+        <v>511</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>82</v>
@@ -10549,10 +10657,10 @@
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>82</v>
+        <v>192</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>192</v>
+        <v>512</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10563,21 +10671,21 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>551</v>
+        <v>513</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>551</v>
+        <v>513</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>82</v>
+        <v>514</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>82</v>
@@ -10589,16 +10697,20 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>552</v>
+        <v>258</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>553</v>
+        <v>515</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
+        <v>516</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>518</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
       </c>
@@ -10622,13 +10734,13 @@
         <v>82</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>82</v>
+        <v>519</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>82</v>
+        <v>520</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>82</v>
@@ -10646,16 +10758,16 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>551</v>
+        <v>513</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>555</v>
+        <v>82</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>105</v>
@@ -10664,27 +10776,27 @@
         <v>82</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>82</v>
+        <v>521</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>556</v>
+        <v>522</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>557</v>
+        <v>523</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>82</v>
+        <v>524</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>558</v>
+        <v>525</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>558</v>
+        <v>525</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10695,7 +10807,7 @@
         <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>82</v>
@@ -10707,16 +10819,20 @@
         <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>552</v>
+        <v>526</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>559</v>
+        <v>527</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="N70" s="2"/>
-      <c r="O70" s="2"/>
+        <v>528</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>530</v>
+      </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
       </c>
@@ -10764,16 +10880,16 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>558</v>
+        <v>525</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>555</v>
+        <v>82</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>105</v>
@@ -10785,10 +10901,10 @@
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>556</v>
+        <v>531</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>561</v>
+        <v>532</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
@@ -10799,10 +10915,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>562</v>
+        <v>533</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>562</v>
+        <v>533</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10825,20 +10941,18 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>563</v>
+        <v>534</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>564</v>
+        <v>535</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>566</v>
-      </c>
+        <v>536</v>
+      </c>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>82</v>
       </c>
@@ -10862,13 +10976,13 @@
         <v>82</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>567</v>
+        <v>537</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>568</v>
+        <v>538</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>82</v>
@@ -10886,7 +11000,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>562</v>
+        <v>533</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10904,27 +11018,27 @@
         <v>82</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>569</v>
+        <v>539</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>570</v>
+        <v>540</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>488</v>
+        <v>541</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>82</v>
+        <v>542</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>571</v>
+        <v>543</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>571</v>
+        <v>543</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10935,7 +11049,7 @@
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>82</v>
@@ -10947,19 +11061,19 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>572</v>
+        <v>544</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>573</v>
+        <v>545</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>574</v>
+        <v>546</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>575</v>
+        <v>547</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>82</v>
@@ -10987,10 +11101,10 @@
         <v>159</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>576</v>
+        <v>548</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>577</v>
+        <v>549</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>82</v>
@@ -11008,13 +11122,13 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>571</v>
+        <v>543</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>82</v>
@@ -11026,13 +11140,13 @@
         <v>82</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>569</v>
+        <v>82</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>570</v>
+        <v>550</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>488</v>
+        <v>551</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
@@ -11043,10 +11157,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>578</v>
+        <v>552</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>578</v>
+        <v>552</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11069,18 +11183,18 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>579</v>
+        <v>553</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>580</v>
+        <v>554</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="N73" s="2"/>
-      <c r="O73" t="s" s="2">
-        <v>582</v>
-      </c>
+        <v>555</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>82</v>
       </c>
@@ -11128,7 +11242,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>578</v>
+        <v>552</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11146,27 +11260,27 @@
         <v>82</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>82</v>
+        <v>557</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>82</v>
+        <v>558</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>583</v>
+        <v>559</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>82</v>
+        <v>560</v>
       </c>
     </row>
-    <row r="74" hidden="true">
+    <row r="74">
       <c r="A74" t="s" s="2">
-        <v>584</v>
+        <v>561</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>584</v>
+        <v>561</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11180,7 +11294,7 @@
         <v>93</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>82</v>
@@ -11189,15 +11303,17 @@
         <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>107</v>
+        <v>562</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>585</v>
+        <v>563</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="N74" s="2"/>
+        <v>564</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>565</v>
+      </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>82</v>
@@ -11246,7 +11362,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>584</v>
+        <v>561</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11264,27 +11380,27 @@
         <v>82</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>82</v>
+        <v>566</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>556</v>
+        <v>567</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>587</v>
+        <v>568</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>82</v>
+        <v>569</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>588</v>
+        <v>570</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>588</v>
+        <v>570</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11304,21 +11420,23 @@
         <v>82</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>589</v>
+        <v>571</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>590</v>
+        <v>572</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>591</v>
+        <v>573</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="O75" s="2"/>
+        <v>574</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>575</v>
+      </c>
       <c r="P75" t="s" s="2">
         <v>82</v>
       </c>
@@ -11366,7 +11484,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>588</v>
+        <v>570</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11378,7 +11496,7 @@
         <v>82</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>105</v>
+        <v>576</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>82</v>
@@ -11387,10 +11505,10 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>593</v>
+        <v>577</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>594</v>
+        <v>578</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11401,10 +11519,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>595</v>
+        <v>579</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>595</v>
+        <v>579</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11415,7 +11533,7 @@
         <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>82</v>
@@ -11424,20 +11542,18 @@
         <v>82</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>596</v>
+        <v>107</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>597</v>
+        <v>108</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>599</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>82</v>
@@ -11486,19 +11602,19 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>595</v>
+        <v>110</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>82</v>
@@ -11507,10 +11623,10 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>593</v>
+        <v>82</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>600</v>
+        <v>111</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
@@ -11519,16 +11635,16 @@
         <v>82</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>601</v>
+        <v>580</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>601</v>
+        <v>580</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11538,29 +11654,27 @@
         <v>81</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>536</v>
+        <v>114</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>602</v>
+        <v>115</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>602</v>
+        <v>116</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>604</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>82</v>
       </c>
@@ -11608,7 +11722,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>601</v>
+        <v>121</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11620,7 +11734,7 @@
         <v>82</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>605</v>
+        <v>122</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>82</v>
@@ -11629,10 +11743,10 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>606</v>
+        <v>82</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>607</v>
+        <v>111</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
@@ -11643,42 +11757,46 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>608</v>
+        <v>581</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>608</v>
+        <v>581</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>82</v>
+        <v>582</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I78" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>108</v>
+        <v>583</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N78" s="2"/>
-      <c r="O78" s="2"/>
+        <v>584</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>216</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>82</v>
       </c>
@@ -11726,19 +11844,19 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>110</v>
+        <v>585</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>82</v>
@@ -11750,7 +11868,7 @@
         <v>82</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>111</v>
+        <v>192</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
@@ -11761,21 +11879,21 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>609</v>
+        <v>586</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>609</v>
+        <v>586</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>82</v>
@@ -11787,17 +11905,15 @@
         <v>82</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>114</v>
+        <v>587</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>115</v>
+        <v>588</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>589</v>
+      </c>
+      <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>82</v>
@@ -11846,19 +11962,19 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>121</v>
+        <v>586</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>82</v>
+        <v>590</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>82</v>
@@ -11867,10 +11983,10 @@
         <v>82</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>82</v>
+        <v>591</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>111</v>
+        <v>592</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
@@ -11881,46 +11997,42 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>610</v>
+        <v>593</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>610</v>
+        <v>593</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>547</v>
+        <v>82</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I80" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>114</v>
+        <v>587</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>548</v>
+        <v>594</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>211</v>
-      </c>
+        <v>595</v>
+      </c>
+      <c r="N80" s="2"/>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>82</v>
       </c>
@@ -11968,19 +12080,19 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>550</v>
+        <v>593</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>82</v>
+        <v>590</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>82</v>
@@ -11989,10 +12101,10 @@
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>82</v>
+        <v>591</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>192</v>
+        <v>596</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
@@ -12001,12 +12113,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>611</v>
+        <v>597</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>611</v>
+        <v>597</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12014,34 +12126,34 @@
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G81" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>612</v>
+        <v>598</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>613</v>
+        <v>599</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>614</v>
+        <v>600</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>615</v>
+        <v>601</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>82</v>
@@ -12066,13 +12178,13 @@
         <v>82</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>342</v>
+        <v>602</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>343</v>
+        <v>603</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>82</v>
@@ -12090,10 +12202,10 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>611</v>
+        <v>597</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH81" t="s" s="2">
         <v>93</v>
@@ -12108,27 +12220,27 @@
         <v>82</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>616</v>
+        <v>604</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>346</v>
+        <v>605</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>347</v>
+        <v>523</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>348</v>
+        <v>82</v>
       </c>
       <c r="AP81" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>617</v>
+        <v>606</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>617</v>
+        <v>606</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12139,31 +12251,31 @@
         <v>80</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>618</v>
+        <v>258</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>619</v>
+        <v>607</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>620</v>
+        <v>608</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>621</v>
+        <v>609</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>418</v>
+        <v>610</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>82</v>
@@ -12188,13 +12300,13 @@
         <v>82</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>623</v>
+        <v>612</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>82</v>
@@ -12212,16 +12324,16 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>617</v>
+        <v>606</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>624</v>
+        <v>82</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>105</v>
@@ -12230,27 +12342,27 @@
         <v>82</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>625</v>
+        <v>604</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>422</v>
+        <v>605</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>423</v>
+        <v>523</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>424</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>626</v>
+        <v>613</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>626</v>
+        <v>613</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12264,7 +12376,7 @@
         <v>93</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>82</v>
@@ -12273,19 +12385,17 @@
         <v>82</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>253</v>
+        <v>614</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>627</v>
+        <v>615</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>629</v>
-      </c>
+        <v>616</v>
+      </c>
+      <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
-        <v>473</v>
+        <v>617</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>82</v>
@@ -12310,13 +12420,13 @@
         <v>82</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>474</v>
+        <v>82</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>475</v>
+        <v>82</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>82</v>
@@ -12334,7 +12444,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>626</v>
+        <v>613</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12343,7 +12453,7 @@
         <v>93</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>630</v>
+        <v>82</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>105</v>
@@ -12355,10 +12465,10 @@
         <v>82</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>192</v>
+        <v>82</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>477</v>
+        <v>618</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
@@ -12369,21 +12479,21 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>631</v>
+        <v>619</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>631</v>
+        <v>619</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>479</v>
+        <v>82</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>82</v>
@@ -12395,20 +12505,16 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>253</v>
+        <v>107</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>480</v>
+        <v>620</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>483</v>
-      </c>
+        <v>621</v>
+      </c>
+      <c r="N84" s="2"/>
+      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>82</v>
       </c>
@@ -12432,13 +12538,13 @@
         <v>82</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>484</v>
+        <v>82</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>485</v>
+        <v>82</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>82</v>
@@ -12456,13 +12562,13 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>631</v>
+        <v>619</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>82</v>
@@ -12474,27 +12580,27 @@
         <v>82</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>486</v>
+        <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>487</v>
+        <v>591</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>488</v>
+        <v>622</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>489</v>
+        <v>82</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>632</v>
+        <v>623</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>632</v>
+        <v>623</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12514,23 +12620,21 @@
         <v>82</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>83</v>
+        <v>624</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>633</v>
+        <v>625</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>540</v>
-      </c>
+        <v>627</v>
+      </c>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>82</v>
       </c>
@@ -12578,7 +12682,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>632</v>
+        <v>623</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12599,20 +12703,1232 @@
         <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>542</v>
+        <v>628</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>543</v>
+        <v>629</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP85" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="86" hidden="true">
+      <c r="A86" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="O86" s="2"/>
+      <c r="P86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="AO86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP86" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="P87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q87" s="2"/>
+      <c r="R87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="AN87" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="AO87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP87" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="88" hidden="true">
+      <c r="A88" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="N88" s="2"/>
+      <c r="O88" s="2"/>
+      <c r="P88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AO88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP88" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="89" hidden="true">
+      <c r="A89" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O89" s="2"/>
+      <c r="P89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q89" s="2"/>
+      <c r="R89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN89" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AO89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP89" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="90" hidden="true">
+      <c r="A90" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="P90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q90" s="2"/>
+      <c r="R90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AO90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP90" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E91" s="2"/>
+      <c r="F91" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K91" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="O91" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="P91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q91" s="2"/>
+      <c r="R91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AO91" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AP91" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="O92" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="P92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q92" s="2"/>
+      <c r="R92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AO92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP92" t="s" s="2">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="O93" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="P93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q93" s="2"/>
+      <c r="R93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="AO93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP93" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="94" hidden="true">
+      <c r="A94" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="O94" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="P94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q94" s="2"/>
+      <c r="R94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="AN94" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AO94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP94" t="s" s="2">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="95" hidden="true">
+      <c r="A95" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E95" s="2"/>
+      <c r="F95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K95" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="O95" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="P95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q95" s="2"/>
+      <c r="R95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF95" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="AN95" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="AO95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP95" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP85">
+  <autoFilter ref="A1:AP95">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -12622,7 +13938,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI84">
+  <conditionalFormatting sqref="A2:AI94">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T08:51:58+00:00</t>
+    <t>2026-01-19T09:23:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:23:14+00:00</t>
+    <t>2026-01-19T09:39:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:39:10+00:00</t>
+    <t>2026-01-19T09:47:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:47:31+00:00</t>
+    <t>2026-01-19T09:54:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:54:18+00:00</t>
+    <t>2026-01-19T09:56:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:56:13+00:00</t>
+    <t>2026-01-19T10:07:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T10:07:50+00:00</t>
+    <t>2026-01-20T07:44:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T07:44:39+00:00</t>
+    <t>2026-01-20T09:11:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T09:11:57+00:00</t>
+    <t>2026-01-20T09:43:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T09:43:53+00:00</t>
+    <t>2026-01-20T09:47:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T09:47:48+00:00</t>
+    <t>2026-01-20T10:06:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T10:06:11+00:00</t>
+    <t>2026-01-20T11:11:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$94</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3675" uniqueCount="670">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3637" uniqueCount="665">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T11:11:06+00:00</t>
+    <t>2026-01-20T12:50:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -665,22 +665,6 @@
   <si>
     <t xml:space="preserve">ele-1
 </t>
-  </si>
-  <si>
-    <t>Observation.extension:MesOriginOfData</t>
-  </si>
-  <si>
-    <t>MesOriginOfData</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-origin-of-data}
-</t>
-  </si>
-  <si>
-    <t>Origine de la donnée</t>
-  </si>
-  <si>
-    <t>Extension pour tracer l'origine de la donnée issue d'un compte rendu de biologie (CR-Bio).</t>
   </si>
   <si>
     <t>Observation.modifierExtension</t>
@@ -2425,7 +2409,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP95"/>
+  <dimension ref="A1:AP94"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="45.484375" customWidth="true" bestFit="true"/>
@@ -4756,41 +4740,43 @@
         <v>208</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="C20" t="s" s="2">
-        <v>209</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="N20" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O20" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="M20" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>82</v>
       </c>
@@ -4838,7 +4824,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4847,7 +4833,7 @@
         <v>81</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>122</v>
@@ -4862,7 +4848,7 @@
         <v>82</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>82</v>
+        <v>192</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>82</v>
@@ -4880,7 +4866,7 @@
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4893,25 +4879,23 @@
         <v>82</v>
       </c>
       <c r="I21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J21" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="J21" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K21" t="s" s="2">
-        <v>114</v>
+        <v>214</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>82</v>
@@ -4960,7 +4944,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4972,22 +4956,22 @@
         <v>82</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>82</v>
+        <v>218</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>82</v>
+        <v>219</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>192</v>
+        <v>220</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>82</v>
+        <v>221</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>82</v>
@@ -4995,14 +4979,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>82</v>
+        <v>223</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -5021,17 +5005,17 @@
         <v>94</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>82</v>
@@ -5080,7 +5064,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -5095,19 +5079,19 @@
         <v>105</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>226</v>
+        <v>82</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>82</v>
@@ -5115,14 +5099,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -5141,18 +5125,18 @@
         <v>94</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N23" s="2"/>
-      <c r="O23" t="s" s="2">
-        <v>232</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>82</v>
       </c>
@@ -5200,7 +5184,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -5215,16 +5199,16 @@
         <v>105</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>82</v>
@@ -5233,46 +5217,48 @@
         <v>82</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>237</v>
+        <v>82</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>238</v>
+        <v>169</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O24" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
       </c>
@@ -5296,13 +5282,11 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y24" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>82</v>
+        <v>246</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
@@ -5320,13 +5304,13 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>82</v>
@@ -5335,30 +5319,30 @@
         <v>105</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>82</v>
+        <v>248</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>82</v>
+        <v>251</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5369,31 +5353,31 @@
         <v>93</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>94</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>169</v>
+        <v>253</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -5418,35 +5402,35 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="Y25" s="2"/>
+        <v>173</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="Z25" t="s" s="2">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="AC25" s="2"/>
       <c r="AD25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>82</v>
@@ -5455,32 +5439,34 @@
         <v>105</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN25" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AO25" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AP25" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="AL25" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="AP25" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="26" hidden="true">
-      <c r="A26" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="C26" s="2"/>
+      <c r="C26" t="s" s="2">
+        <v>264</v>
+      </c>
       <c r="D26" t="s" s="2">
         <v>82</v>
       </c>
@@ -5489,7 +5475,7 @@
         <v>93</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>94</v>
@@ -5501,19 +5487,19 @@
         <v>82</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -5541,26 +5527,28 @@
         <v>173</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="AC26" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5584,37 +5572,35 @@
         <v>82</v>
       </c>
       <c r="AN26" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AO26" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AP26" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="27" hidden="true">
+      <c r="A27" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="B27" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="AO26" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="AP26" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="C27" t="s" s="2">
-        <v>269</v>
-      </c>
+      <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>82</v>
@@ -5623,20 +5609,16 @@
         <v>82</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>258</v>
+        <v>107</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>259</v>
+        <v>108</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>262</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>82</v>
       </c>
@@ -5660,13 +5642,13 @@
         <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>173</v>
+        <v>82</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>263</v>
+        <v>82</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>264</v>
+        <v>82</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
@@ -5684,19 +5666,19 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>257</v>
+        <v>110</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>82</v>
@@ -5708,10 +5690,10 @@
         <v>82</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>266</v>
+        <v>111</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>267</v>
+        <v>82</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>82</v>
@@ -5719,21 +5701,21 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>82</v>
@@ -5745,15 +5727,17 @@
         <v>82</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5790,31 +5774,31 @@
         <v>82</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>82</v>
@@ -5835,46 +5819,48 @@
         <v>82</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>114</v>
+        <v>147</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>115</v>
+        <v>271</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>116</v>
+        <v>272</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>274</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
       </c>
@@ -5910,19 +5896,19 @@
         <v>82</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>121</v>
+        <v>275</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5934,7 +5920,7 @@
         <v>82</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>82</v>
@@ -5943,10 +5929,10 @@
         <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>82</v>
+        <v>276</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>111</v>
+        <v>277</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
@@ -5955,12 +5941,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5968,35 +5954,31 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G30" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G30" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="H30" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>147</v>
+        <v>107</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>276</v>
+        <v>108</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>279</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>82</v>
       </c>
@@ -6044,19 +6026,19 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>280</v>
+        <v>110</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>82</v>
@@ -6065,10 +6047,10 @@
         <v>82</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>281</v>
+        <v>82</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>282</v>
+        <v>111</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
@@ -6079,21 +6061,21 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>82</v>
@@ -6105,15 +6087,17 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -6150,31 +6134,31 @@
         <v>82</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>82</v>
@@ -6195,52 +6179,54 @@
         <v>82</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>115</v>
+        <v>284</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>116</v>
+        <v>285</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O32" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>287</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>82</v>
+        <v>288</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>82</v>
@@ -6270,31 +6256,31 @@
         <v>82</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>121</v>
+        <v>289</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>82</v>
@@ -6303,10 +6289,10 @@
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>82</v>
+        <v>290</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>111</v>
+        <v>291</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
@@ -6315,12 +6301,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6328,13 +6314,13 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>82</v>
@@ -6343,26 +6329,24 @@
         <v>94</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>292</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>293</v>
+        <v>82</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>82</v>
@@ -6404,7 +6388,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6425,10 +6409,10 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -6437,12 +6421,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6450,13 +6434,13 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>82</v>
@@ -6465,24 +6449,24 @@
         <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>107</v>
+        <v>169</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="O34" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>82</v>
+        <v>305</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>82</v>
@@ -6524,7 +6508,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6545,10 +6529,10 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -6557,12 +6541,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6570,13 +6554,13 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>82</v>
@@ -6585,24 +6569,24 @@
         <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>169</v>
+        <v>107</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>310</v>
+        <v>82</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>82</v>
@@ -6644,7 +6628,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6665,10 +6649,10 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6679,10 +6663,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6705,17 +6689,19 @@
         <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>107</v>
+        <v>319</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>321</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>322</v>
+      </c>
       <c r="O36" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6764,7 +6750,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6785,10 +6771,10 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6799,10 +6785,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6825,19 +6811,19 @@
         <v>94</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>324</v>
+        <v>107</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6886,7 +6872,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6907,10 +6893,10 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6919,26 +6905,26 @@
         <v>82</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>82</v>
+        <v>337</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>82</v>
@@ -6947,19 +6933,19 @@
         <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>107</v>
+        <v>253</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -6984,13 +6970,13 @@
         <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>82</v>
+        <v>342</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>82</v>
+        <v>343</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>82</v>
@@ -7008,10 +6994,10 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>93</v>
@@ -7023,66 +7009,62 @@
         <v>105</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>82</v>
+        <v>344</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>82</v>
+        <v>345</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>82</v>
+        <v>348</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>82</v>
+        <v>349</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>342</v>
+        <v>82</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>258</v>
+        <v>107</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>343</v>
+        <v>108</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>346</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>82</v>
       </c>
@@ -7106,13 +7088,13 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>347</v>
+        <v>82</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>348</v>
+        <v>82</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -7130,10 +7112,10 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>341</v>
+        <v>110</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>93</v>
@@ -7142,44 +7124,44 @@
         <v>82</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>349</v>
+        <v>82</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>350</v>
+        <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>351</v>
+        <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>352</v>
+        <v>111</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>353</v>
+        <v>82</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>354</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>82</v>
@@ -7191,15 +7173,17 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -7236,31 +7220,31 @@
         <v>82</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>82</v>
@@ -7283,18 +7267,18 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>80</v>
+        <v>353</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>81</v>
@@ -7306,21 +7290,23 @@
         <v>82</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>114</v>
+        <v>147</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>115</v>
+        <v>271</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>116</v>
+        <v>272</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>274</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
@@ -7356,11 +7342,9 @@
         <v>82</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>119</v>
-      </c>
+        <v>354</v>
+      </c>
+      <c r="AC41" s="2"/>
       <c r="AD41" t="s" s="2">
         <v>82</v>
       </c>
@@ -7368,7 +7352,7 @@
         <v>120</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>121</v>
+        <v>275</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7380,7 +7364,7 @@
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>82</v>
@@ -7389,10 +7373,10 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>82</v>
+        <v>276</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>111</v>
+        <v>277</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7403,21 +7387,23 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="C42" s="2"/>
+        <v>352</v>
+      </c>
+      <c r="C42" t="s" s="2">
+        <v>356</v>
+      </c>
       <c r="D42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>358</v>
+        <v>93</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
@@ -7432,16 +7418,16 @@
         <v>147</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -7478,17 +7464,19 @@
         <v>82</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="AC42" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7509,10 +7497,10 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -7523,20 +7511,18 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="C43" t="s" s="2">
-        <v>361</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>93</v>
@@ -7548,23 +7534,19 @@
         <v>82</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>147</v>
+        <v>107</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>276</v>
+        <v>108</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>279</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>82</v>
       </c>
@@ -7612,19 +7594,19 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>280</v>
+        <v>110</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>82</v>
@@ -7633,10 +7615,10 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>281</v>
+        <v>82</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>282</v>
+        <v>111</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7647,21 +7629,21 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>82</v>
@@ -7673,15 +7655,17 @@
         <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7718,31 +7702,31 @@
         <v>82</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>82</v>
@@ -7765,21 +7749,21 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>82</v>
@@ -7788,27 +7772,29 @@
         <v>82</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>115</v>
+        <v>284</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>116</v>
+        <v>285</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>287</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>82</v>
+        <v>363</v>
       </c>
       <c r="S45" t="s" s="2">
         <v>82</v>
@@ -7838,31 +7824,31 @@
         <v>82</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>121</v>
+        <v>289</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
@@ -7871,10 +7857,10 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>82</v>
+        <v>290</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>111</v>
+        <v>291</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7885,10 +7871,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7896,7 +7882,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>93</v>
@@ -7911,26 +7897,24 @@
         <v>94</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>292</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>368</v>
+        <v>82</v>
       </c>
       <c r="S46" t="s" s="2">
         <v>82</v>
@@ -7972,7 +7956,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7993,10 +7977,10 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -8007,10 +7991,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8018,7 +8002,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>93</v>
@@ -8033,24 +8017,24 @@
         <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>107</v>
+        <v>169</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>82</v>
+        <v>368</v>
       </c>
       <c r="S47" t="s" s="2">
         <v>82</v>
@@ -8092,7 +8076,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -8113,10 +8097,10 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -8127,10 +8111,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8138,7 +8122,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>93</v>
@@ -8153,24 +8137,24 @@
         <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>169</v>
+        <v>107</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>373</v>
+        <v>82</v>
       </c>
       <c r="S48" t="s" s="2">
         <v>82</v>
@@ -8212,7 +8196,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8233,10 +8217,10 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -8247,10 +8231,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8273,17 +8257,19 @@
         <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>107</v>
+        <v>319</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>321</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>322</v>
+      </c>
       <c r="O49" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -8332,7 +8318,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8353,10 +8339,10 @@
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8367,18 +8353,20 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="C50" s="2"/>
+        <v>352</v>
+      </c>
+      <c r="C50" t="s" s="2">
+        <v>374</v>
+      </c>
       <c r="D50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>93</v>
@@ -8393,19 +8381,19 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>324</v>
+        <v>147</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>325</v>
+        <v>271</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>326</v>
+        <v>272</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>327</v>
+        <v>273</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>328</v>
+        <v>274</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -8415,7 +8403,7 @@
         <v>82</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>82</v>
+        <v>375</v>
       </c>
       <c r="T50" t="s" s="2">
         <v>82</v>
@@ -8454,13 +8442,13 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>329</v>
+        <v>275</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>82</v>
@@ -8475,10 +8463,10 @@
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>330</v>
+        <v>276</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>331</v>
+        <v>277</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8489,20 +8477,18 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="C51" t="s" s="2">
-        <v>379</v>
-      </c>
+        <v>376</v>
+      </c>
+      <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>93</v>
@@ -8517,19 +8503,19 @@
         <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>147</v>
+        <v>107</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>276</v>
+        <v>329</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>277</v>
+        <v>330</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>278</v>
+        <v>331</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>279</v>
+        <v>332</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8539,7 +8525,7 @@
         <v>82</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>380</v>
+        <v>82</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>82</v>
@@ -8578,13 +8564,13 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>280</v>
+        <v>333</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>82</v>
@@ -8599,10 +8585,10 @@
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>281</v>
+        <v>334</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>282</v>
+        <v>335</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8611,12 +8597,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8624,13 +8610,13 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>82</v>
@@ -8639,19 +8625,19 @@
         <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>107</v>
+        <v>378</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>335</v>
+        <v>380</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>336</v>
+        <v>381</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>337</v>
+        <v>382</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8700,7 +8686,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>338</v>
+        <v>377</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8715,30 +8701,30 @@
         <v>105</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>82</v>
+        <v>383</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>339</v>
+        <v>384</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>340</v>
+        <v>385</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>82</v>
+        <v>386</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8746,13 +8732,13 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>82</v>
@@ -8761,20 +8747,18 @@
         <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>387</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>82</v>
       </c>
@@ -8822,13 +8806,13 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>82</v>
@@ -8837,19 +8821,19 @@
         <v>105</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>388</v>
+        <v>82</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>389</v>
+        <v>346</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>82</v>
@@ -8857,21 +8841,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>82</v>
+        <v>394</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>82</v>
@@ -8883,18 +8867,20 @@
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>398</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>399</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
       </c>
@@ -8942,13 +8928,13 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>82</v>
@@ -8957,44 +8943,44 @@
         <v>105</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>82</v>
+        <v>400</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>351</v>
+        <v>401</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>82</v>
@@ -9003,19 +8989,19 @@
         <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -9064,7 +9050,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -9073,50 +9059,50 @@
         <v>93</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>82</v>
+        <v>411</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>105</v>
+        <v>412</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>410</v>
+        <v>82</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>82</v>
@@ -9125,20 +9111,18 @@
         <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>411</v>
+        <v>129</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>415</v>
-      </c>
+        <v>420</v>
+      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>82</v>
       </c>
@@ -9186,7 +9170,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9195,25 +9179,25 @@
         <v>93</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>416</v>
+        <v>82</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>417</v>
+        <v>105</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>418</v>
+        <v>82</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>82</v>
@@ -9221,10 +9205,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9235,7 +9219,7 @@
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>82</v>
@@ -9247,18 +9231,18 @@
         <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>129</v>
+        <v>425</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="O57" s="2"/>
+        <v>427</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" t="s" s="2">
+        <v>428</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
       </c>
@@ -9306,13 +9290,13 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>82</v>
@@ -9321,19 +9305,19 @@
         <v>105</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>82</v>
+        <v>429</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>82</v>
@@ -9341,10 +9325,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9355,10 +9339,10 @@
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>82</v>
@@ -9367,17 +9351,19 @@
         <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>435</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>436</v>
+      </c>
       <c r="O58" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9414,59 +9400,59 @@
         <v>82</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>438</v>
+      </c>
+      <c r="AC58" s="2"/>
       <c r="AD58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>82</v>
+        <v>439</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>82</v>
+        <v>440</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>434</v>
+        <v>82</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>82</v>
+        <v>441</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>437</v>
+        <v>82</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>82</v>
+        <v>444</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="C59" s="2"/>
+        <v>433</v>
+      </c>
+      <c r="C59" t="s" s="2">
+        <v>446</v>
+      </c>
       <c r="D59" t="s" s="2">
         <v>82</v>
       </c>
@@ -9487,19 +9473,19 @@
         <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9536,17 +9522,19 @@
         <v>82</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="AC59" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>444</v>
+        <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9555,7 +9543,7 @@
         <v>93</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>105</v>
@@ -9564,31 +9552,29 @@
         <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="AM59" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP59" t="s" s="2">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="60" hidden="true">
+      <c r="A60" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="AN59" t="s" s="2">
+      <c r="B60" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="AO59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP59" t="s" s="2">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="C60" t="s" s="2">
-        <v>451</v>
-      </c>
+      <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
         <v>82</v>
       </c>
@@ -9600,29 +9586,25 @@
         <v>93</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>439</v>
+        <v>107</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>440</v>
+        <v>108</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>442</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>82</v>
       </c>
@@ -9670,7 +9652,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>438</v>
+        <v>110</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9679,47 +9661,47 @@
         <v>93</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>445</v>
+        <v>82</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>446</v>
+        <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>447</v>
+        <v>82</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>448</v>
+        <v>111</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>449</v>
+        <v>82</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>82</v>
@@ -9731,15 +9713,17 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9776,31 +9760,31 @@
         <v>82</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>82</v>
@@ -9821,46 +9805,48 @@
         <v>82</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>114</v>
+        <v>453</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>115</v>
+        <v>454</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>116</v>
+        <v>455</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>456</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>457</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>82</v>
       </c>
@@ -9896,31 +9882,31 @@
         <v>82</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>121</v>
+        <v>458</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>82</v>
@@ -9929,10 +9915,10 @@
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>82</v>
+        <v>459</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>111</v>
+        <v>460</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
@@ -9941,12 +9927,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9954,39 +9940,39 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I63" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="I63" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="J63" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>458</v>
+        <v>169</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>461</v>
-      </c>
+        <v>464</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q63" s="2"/>
+      <c r="Q63" t="s" s="2">
+        <v>466</v>
+      </c>
       <c r="R63" t="s" s="2">
         <v>82</v>
       </c>
@@ -10006,13 +9992,13 @@
         <v>82</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>82</v>
+        <v>245</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>82</v>
+        <v>467</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>82</v>
+        <v>468</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>82</v>
@@ -10030,7 +10016,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -10051,10 +10037,10 @@
         <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -10063,12 +10049,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10076,44 +10062,42 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J64" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>169</v>
+        <v>107</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q64" t="s" s="2">
-        <v>471</v>
-      </c>
+      <c r="Q64" s="2"/>
       <c r="R64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="S64" t="s" s="2">
-        <v>82</v>
+        <v>477</v>
       </c>
       <c r="T64" t="s" s="2">
         <v>82</v>
@@ -10128,13 +10112,13 @@
         <v>82</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>250</v>
+        <v>82</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>472</v>
+        <v>82</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>473</v>
+        <v>82</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>82</v>
@@ -10152,7 +10136,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10173,10 +10157,10 @@
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
@@ -10187,10 +10171,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10213,27 +10197,27 @@
         <v>94</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
-        <v>82</v>
+        <v>486</v>
       </c>
       <c r="S65" t="s" s="2">
-        <v>482</v>
+        <v>82</v>
       </c>
       <c r="T65" t="s" s="2">
         <v>82</v>
@@ -10272,7 +10256,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10281,7 +10265,7 @@
         <v>93</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>82</v>
+        <v>488</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>105</v>
@@ -10293,10 +10277,10 @@
         <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -10307,10 +10291,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10333,27 +10317,29 @@
         <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>135</v>
+        <v>169</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>492</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>493</v>
+      </c>
       <c r="O66" t="s" s="2">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q66" s="2"/>
       <c r="R66" t="s" s="2">
-        <v>491</v>
+        <v>82</v>
       </c>
       <c r="S66" t="s" s="2">
-        <v>82</v>
+        <v>477</v>
       </c>
       <c r="T66" t="s" s="2">
         <v>82</v>
@@ -10368,13 +10354,13 @@
         <v>82</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>82</v>
+        <v>245</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>82</v>
+        <v>495</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>82</v>
+        <v>496</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>82</v>
@@ -10392,7 +10378,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10401,7 +10387,7 @@
         <v>93</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>493</v>
+        <v>82</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>105</v>
@@ -10413,10 +10399,10 @@
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
@@ -10427,10 +10413,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10438,7 +10424,7 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>93</v>
@@ -10450,22 +10436,22 @@
         <v>82</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>169</v>
+        <v>253</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
@@ -10475,7 +10461,7 @@
         <v>82</v>
       </c>
       <c r="S67" t="s" s="2">
-        <v>482</v>
+        <v>82</v>
       </c>
       <c r="T67" t="s" s="2">
         <v>82</v>
@@ -10490,13 +10476,13 @@
         <v>82</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>250</v>
+        <v>151</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>82</v>
@@ -10514,7 +10500,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10523,7 +10509,7 @@
         <v>93</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>82</v>
+        <v>506</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>105</v>
@@ -10535,10 +10521,10 @@
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>484</v>
+        <v>192</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10547,26 +10533,26 @@
         <v>82</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>82</v>
+        <v>509</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>82</v>
@@ -10575,19 +10561,19 @@
         <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
@@ -10615,10 +10601,10 @@
         <v>151</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>82</v>
@@ -10636,16 +10622,16 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>511</v>
+        <v>82</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>105</v>
@@ -10654,31 +10640,31 @@
         <v>82</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>82</v>
+        <v>516</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>192</v>
+        <v>517</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>82</v>
+        <v>519</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>514</v>
+        <v>82</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10697,19 +10683,19 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>258</v>
+        <v>521</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
@@ -10734,31 +10720,31 @@
         <v>82</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>519</v>
+        <v>82</v>
       </c>
       <c r="Z69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF69" t="s" s="2">
         <v>520</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>513</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10776,27 +10762,27 @@
         <v>82</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>521</v>
+        <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>524</v>
+        <v>82</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10807,7 +10793,7 @@
         <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>82</v>
@@ -10819,20 +10805,18 @@
         <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>526</v>
+        <v>253</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>530</v>
-      </c>
+        <v>531</v>
+      </c>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>82</v>
       </c>
@@ -10856,13 +10840,13 @@
         <v>82</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>82</v>
+        <v>159</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>82</v>
+        <v>532</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>82</v>
+        <v>533</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>82</v>
@@ -10880,13 +10864,13 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>82</v>
@@ -10898,27 +10882,27 @@
         <v>82</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>82</v>
+        <v>534</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>82</v>
+        <v>537</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10941,18 +10925,20 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="O71" s="2"/>
+        <v>541</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>542</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>82</v>
       </c>
@@ -10979,28 +10965,28 @@
         <v>159</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="Z71" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF71" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -11018,27 +11004,27 @@
         <v>82</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>539</v>
+        <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>542</v>
+        <v>82</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11061,20 +11047,18 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>258</v>
+        <v>548</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>547</v>
-      </c>
+        <v>551</v>
+      </c>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>82</v>
       </c>
@@ -11098,13 +11082,13 @@
         <v>82</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>159</v>
+        <v>82</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>548</v>
+        <v>82</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>549</v>
+        <v>82</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>82</v>
@@ -11122,7 +11106,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -11140,27 +11124,27 @@
         <v>82</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>82</v>
+        <v>552</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>82</v>
+        <v>555</v>
       </c>
     </row>
-    <row r="73" hidden="true">
+    <row r="73">
       <c r="A73" t="s" s="2">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11174,7 +11158,7 @@
         <v>93</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>82</v>
@@ -11183,16 +11167,16 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11242,7 +11226,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11260,27 +11244,27 @@
         <v>82</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>560</v>
+        <v>564</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11291,10 +11275,10 @@
         <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>82</v>
@@ -11303,18 +11287,20 @@
         <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="O74" s="2"/>
+        <v>569</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>570</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>82</v>
       </c>
@@ -11362,45 +11348,45 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>105</v>
+        <v>571</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>566</v>
+        <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>569</v>
+        <v>82</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11411,7 +11397,7 @@
         <v>80</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>82</v>
@@ -11423,20 +11409,16 @@
         <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>571</v>
+        <v>107</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>572</v>
+        <v>108</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>575</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>82</v>
       </c>
@@ -11484,19 +11466,19 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>570</v>
+        <v>110</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>576</v>
+        <v>82</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>82</v>
@@ -11505,10 +11487,10 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>577</v>
+        <v>82</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>578</v>
+        <v>111</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11519,21 +11501,21 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>82</v>
@@ -11545,15 +11527,17 @@
         <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N76" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>82</v>
@@ -11602,19 +11586,19 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>82</v>
@@ -11637,14 +11621,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>113</v>
+        <v>577</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11657,24 +11641,26 @@
         <v>82</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K77" t="s" s="2">
         <v>114</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>115</v>
+        <v>578</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>116</v>
+        <v>579</v>
       </c>
       <c r="N77" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="O77" s="2"/>
+      <c r="O77" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>82</v>
       </c>
@@ -11722,7 +11708,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>121</v>
+        <v>580</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11746,7 +11732,7 @@
         <v>82</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>111</v>
+        <v>192</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
@@ -11764,26 +11750,26 @@
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>582</v>
+        <v>82</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I78" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>114</v>
+        <v>582</v>
       </c>
       <c r="L78" t="s" s="2">
         <v>583</v>
@@ -11791,12 +11777,8 @@
       <c r="M78" t="s" s="2">
         <v>584</v>
       </c>
-      <c r="N78" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>216</v>
-      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>82</v>
       </c>
@@ -11844,19 +11826,19 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI78" t="s" s="2">
         <v>585</v>
       </c>
-      <c r="AG78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI78" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AJ78" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>82</v>
@@ -11865,10 +11847,10 @@
         <v>82</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>82</v>
+        <v>586</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>192</v>
+        <v>587</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
@@ -11879,10 +11861,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11905,13 +11887,13 @@
         <v>82</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11962,7 +11944,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11971,7 +11953,7 @@
         <v>93</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>105</v>
@@ -11983,10 +11965,10 @@
         <v>82</v>
       </c>
       <c r="AM79" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="AN79" t="s" s="2">
         <v>591</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>592</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
@@ -11997,10 +11979,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12023,16 +12005,20 @@
         <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>587</v>
+        <v>253</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>594</v>
       </c>
-      <c r="M80" t="s" s="2">
+      <c r="N80" t="s" s="2">
         <v>595</v>
       </c>
-      <c r="N80" s="2"/>
-      <c r="O80" s="2"/>
+      <c r="O80" t="s" s="2">
+        <v>596</v>
+      </c>
       <c r="P80" t="s" s="2">
         <v>82</v>
       </c>
@@ -12056,13 +12042,13 @@
         <v>82</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>82</v>
+        <v>173</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>82</v>
+        <v>597</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>82</v>
+        <v>598</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>82</v>
@@ -12080,7 +12066,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -12089,7 +12075,7 @@
         <v>93</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>590</v>
+        <v>82</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>105</v>
@@ -12098,13 +12084,13 @@
         <v>82</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>82</v>
+        <v>599</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>591</v>
+        <v>600</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>596</v>
+        <v>518</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
@@ -12115,10 +12101,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12129,7 +12115,7 @@
         <v>80</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>82</v>
@@ -12141,19 +12127,19 @@
         <v>82</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>82</v>
@@ -12178,13 +12164,13 @@
         <v>82</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>82</v>
@@ -12202,13 +12188,13 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>82</v>
@@ -12220,13 +12206,13 @@
         <v>82</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
@@ -12237,10 +12223,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12251,7 +12237,7 @@
         <v>80</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>82</v>
@@ -12263,19 +12249,17 @@
         <v>82</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>258</v>
+        <v>609</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>609</v>
-      </c>
+        <v>611</v>
+      </c>
+      <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>82</v>
@@ -12300,13 +12284,13 @@
         <v>82</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>159</v>
+        <v>82</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>611</v>
+        <v>82</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>612</v>
+        <v>82</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>82</v>
@@ -12324,13 +12308,13 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>82</v>
@@ -12342,13 +12326,13 @@
         <v>82</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>604</v>
+        <v>82</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>605</v>
+        <v>82</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>523</v>
+        <v>613</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
@@ -12359,10 +12343,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12385,7 +12369,7 @@
         <v>82</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>614</v>
+        <v>107</v>
       </c>
       <c r="L83" t="s" s="2">
         <v>615</v>
@@ -12394,9 +12378,7 @@
         <v>616</v>
       </c>
       <c r="N83" s="2"/>
-      <c r="O83" t="s" s="2">
-        <v>617</v>
-      </c>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>82</v>
       </c>
@@ -12444,7 +12426,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12465,10 +12447,10 @@
         <v>82</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>82</v>
+        <v>586</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
@@ -12479,10 +12461,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12493,7 +12475,7 @@
         <v>80</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>82</v>
@@ -12502,10 +12484,10 @@
         <v>82</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>107</v>
+        <v>619</v>
       </c>
       <c r="L84" t="s" s="2">
         <v>620</v>
@@ -12513,7 +12495,9 @@
       <c r="M84" t="s" s="2">
         <v>621</v>
       </c>
-      <c r="N84" s="2"/>
+      <c r="N84" t="s" s="2">
+        <v>622</v>
+      </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>82</v>
@@ -12562,13 +12546,13 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>82</v>
@@ -12583,10 +12567,10 @@
         <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>591</v>
+        <v>623</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
@@ -12597,10 +12581,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12623,16 +12607,16 @@
         <v>94</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12682,7 +12666,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12703,10 +12687,10 @@
         <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
@@ -12715,12 +12699,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="86" hidden="true">
+    <row r="86">
       <c r="A86" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12734,7 +12718,7 @@
         <v>81</v>
       </c>
       <c r="H86" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I86" t="s" s="2">
         <v>82</v>
@@ -12743,18 +12727,20 @@
         <v>94</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>631</v>
+        <v>566</v>
       </c>
       <c r="L86" t="s" s="2">
         <v>632</v>
       </c>
       <c r="M86" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="N86" t="s" s="2">
         <v>633</v>
       </c>
-      <c r="N86" t="s" s="2">
+      <c r="O86" t="s" s="2">
         <v>634</v>
       </c>
-      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>82</v>
       </c>
@@ -12802,7 +12788,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12814,7 +12800,7 @@
         <v>82</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>105</v>
+        <v>635</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>82</v>
@@ -12823,10 +12809,10 @@
         <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>628</v>
+        <v>636</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
@@ -12835,12 +12821,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12851,32 +12837,28 @@
         <v>80</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>571</v>
+        <v>107</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>637</v>
+        <v>108</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>639</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>82</v>
       </c>
@@ -12924,19 +12906,19 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>636</v>
+        <v>110</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>640</v>
+        <v>82</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>82</v>
@@ -12945,10 +12927,10 @@
         <v>82</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>641</v>
+        <v>82</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>642</v>
+        <v>111</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>82</v>
@@ -12959,21 +12941,21 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>82</v>
@@ -12985,15 +12967,17 @@
         <v>82</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N88" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>82</v>
@@ -13042,19 +13026,19 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>82</v>
@@ -13077,14 +13061,14 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>113</v>
+        <v>577</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -13097,24 +13081,26 @@
         <v>82</v>
       </c>
       <c r="I89" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K89" t="s" s="2">
         <v>114</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>115</v>
+        <v>578</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>116</v>
+        <v>579</v>
       </c>
       <c r="N89" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="O89" s="2"/>
+      <c r="O89" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="P89" t="s" s="2">
         <v>82</v>
       </c>
@@ -13162,7 +13148,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>121</v>
+        <v>580</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -13186,7 +13172,7 @@
         <v>82</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>111</v>
+        <v>192</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
@@ -13195,47 +13181,47 @@
         <v>82</v>
       </c>
     </row>
-    <row r="90" hidden="true">
+    <row r="90">
       <c r="A90" t="s" s="2">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>582</v>
+        <v>82</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J90" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>114</v>
+        <v>253</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>583</v>
+        <v>642</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>584</v>
+        <v>643</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>117</v>
+        <v>644</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>216</v>
+        <v>645</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>82</v>
@@ -13260,13 +13246,13 @@
         <v>82</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>82</v>
+        <v>342</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>82</v>
+        <v>343</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>82</v>
@@ -13284,34 +13270,34 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>585</v>
+        <v>641</v>
       </c>
       <c r="AG90" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>82</v>
+        <v>646</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>82</v>
+        <v>346</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>192</v>
+        <v>347</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>82</v>
+        <v>348</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>82</v>
@@ -13319,10 +13305,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13330,7 +13316,7 @@
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G91" t="s" s="2">
         <v>93</v>
@@ -13345,19 +13331,19 @@
         <v>94</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>258</v>
+        <v>648</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>650</v>
+        <v>437</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>82</v>
@@ -13385,10 +13371,10 @@
         <v>151</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>347</v>
+        <v>652</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>348</v>
+        <v>653</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>82</v>
@@ -13406,16 +13392,16 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH91" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>82</v>
+        <v>654</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>105</v>
@@ -13424,27 +13410,27 @@
         <v>82</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>351</v>
+        <v>442</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>352</v>
+        <v>443</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>353</v>
+        <v>82</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>82</v>
+        <v>444</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13464,22 +13450,22 @@
         <v>82</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>653</v>
+        <v>253</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>442</v>
+        <v>503</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>82</v>
@@ -13507,10 +13493,10 @@
         <v>151</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>657</v>
+        <v>504</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>658</v>
+        <v>505</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>82</v>
@@ -13528,7 +13514,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13537,7 +13523,7 @@
         <v>93</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>105</v>
@@ -13546,22 +13532,22 @@
         <v>82</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>660</v>
+        <v>82</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>447</v>
+        <v>192</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>448</v>
+        <v>507</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>449</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
         <v>661</v>
       </c>
@@ -13570,17 +13556,17 @@
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>82</v>
+        <v>509</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I93" t="s" s="2">
         <v>82</v>
@@ -13589,19 +13575,19 @@
         <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>662</v>
+        <v>510</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>663</v>
+        <v>511</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>664</v>
+        <v>512</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>82</v>
@@ -13629,10 +13615,10 @@
         <v>151</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>82</v>
@@ -13656,10 +13642,10 @@
         <v>80</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>665</v>
+        <v>82</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>105</v>
@@ -13668,31 +13654,31 @@
         <v>82</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>82</v>
+        <v>516</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>192</v>
+        <v>517</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>82</v>
+        <v>519</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>514</v>
+        <v>82</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -13711,19 +13697,19 @@
         <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>258</v>
+        <v>83</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>515</v>
+        <v>663</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>516</v>
+        <v>664</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>517</v>
+        <v>569</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>518</v>
+        <v>570</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>82</v>
@@ -13748,13 +13734,13 @@
         <v>82</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>519</v>
+        <v>82</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>520</v>
+        <v>82</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>82</v>
@@ -13772,7 +13758,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13790,145 +13776,23 @@
         <v>82</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>521</v>
+        <v>82</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>522</v>
+        <v>572</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>523</v>
+        <v>573</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="95" hidden="true">
-      <c r="A95" t="s" s="2">
-        <v>667</v>
-      </c>
-      <c r="B95" t="s" s="2">
-        <v>667</v>
-      </c>
-      <c r="C95" s="2"/>
-      <c r="D95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E95" s="2"/>
-      <c r="F95" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K95" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L95" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="P95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q95" s="2"/>
-      <c r="R95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF95" t="s" s="2">
-        <v>667</v>
-      </c>
-      <c r="AG95" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ95" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM95" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="AO95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP95" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP95">
+  <autoFilter ref="A1:AP94">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -13938,7 +13802,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI94">
+  <conditionalFormatting sqref="A2:AI93">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
